--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\cs-tools\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B36E0F6-BA91-4D21-8139-4B37EC827DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EFF942-ED6A-422F-B8EA-DF097D994507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="5400" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="162">
   <si>
     <t>Wizards</t>
   </si>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -596,6 +596,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:F362"/>
+  <dimension ref="A1:F375"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -8181,6 +8184,266 @@
         <v>46081</v>
       </c>
     </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F363" s="3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F364" s="3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F365" s="5">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E366" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F366" s="5">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E367" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F367" s="3">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E368" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F368" s="5">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E369" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F369" s="3">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F370" s="5">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E371" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F371" s="3">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E372" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F372" s="3">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F373" s="5">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F374" s="5">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F375" s="5">
+        <v>46102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EFF942-ED6A-422F-B8EA-DF097D994507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF945DA-A2A1-4EEF-AAE0-318AF0F42255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="163">
   <si>
     <t>Wizards</t>
   </si>
@@ -522,13 +522,16 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Cache</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +549,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -583,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -596,9 +605,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:F375"/>
+  <dimension ref="A1:F392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -8217,7 +8234,7 @@
       <c r="D364" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E364" s="6" t="s">
+      <c r="E364" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F364" s="3">
@@ -8277,7 +8294,7 @@
       <c r="D367" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E367" s="6" t="s">
+      <c r="E367" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F367" s="3">
@@ -8317,7 +8334,7 @@
       <c r="D369" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E369" s="6" t="s">
+      <c r="E369" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F369" s="3">
@@ -8357,7 +8374,7 @@
       <c r="D371" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E371" s="6" t="s">
+      <c r="E371" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F371" s="3">
@@ -8377,7 +8394,7 @@
       <c r="D372" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E372" s="6" t="s">
+      <c r="E372" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F372" s="3">
@@ -8425,23 +8442,363 @@
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" s="4" t="s">
+      <c r="A375" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="B375" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C375" s="4" t="s">
+      <c r="C375" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D375" s="4" t="s">
+      <c r="D375" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E375" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F375" s="5">
+      <c r="E375" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F375" s="10">
         <v>46102</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F376" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D377" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F377" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F378" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C379" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D379" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E379" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F379" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B380" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C380" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D380" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E380" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F380" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A381" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B381" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C381" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D381" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E381" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F381" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A382" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F382" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A383" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F383" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A384" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B384" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C384" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D384" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E384" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F384" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A385" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B385" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C385" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D385" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E385" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F385" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A386" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B386" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C386" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D386" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E386" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F386" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A387" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F387" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A388" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F388" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A389" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E389" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F389" s="8">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A390" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B390" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C390" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D390" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E390" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F390" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A391" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B391" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C391" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D391" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E391" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F391" s="10">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A392" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B392" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C392" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D392" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E392" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F392" s="10">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF945DA-A2A1-4EEF-AAE0-318AF0F42255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C7623C-9BAE-455B-BBDF-0B151D1F8DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="163">
   <si>
     <t>Wizards</t>
   </si>
@@ -608,14 +608,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:F392"/>
+  <dimension ref="A1:F399"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -8442,22 +8442,22 @@
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" s="9" t="s">
+      <c r="A375" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B375" s="9" t="s">
+      <c r="B375" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C375" s="9" t="s">
+      <c r="C375" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D375" s="9" t="s">
+      <c r="D375" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E375" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F375" s="10">
+      <c r="E375" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F375" s="9">
         <v>46102</v>
       </c>
     </row>
@@ -8474,10 +8474,10 @@
       <c r="D376" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E376" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F376" s="8">
+      <c r="E376" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F376" s="7">
         <v>46143</v>
       </c>
     </row>
@@ -8494,10 +8494,10 @@
       <c r="D377" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E377" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F377" s="8">
+      <c r="E377" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F377" s="7">
         <v>46143</v>
       </c>
     </row>
@@ -8514,70 +8514,70 @@
       <c r="D378" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E378" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F378" s="8">
+      <c r="E378" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F378" s="7">
         <v>46143</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A379" s="9" t="s">
+      <c r="A379" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C379" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D379" s="9" t="s">
+      <c r="C379" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D379" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E379" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F379" s="10">
+      <c r="E379" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F379" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A380" s="9" t="s">
+      <c r="A380" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B380" s="9" t="s">
+      <c r="B380" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C380" s="9" t="s">
+      <c r="C380" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D380" s="9" t="s">
+      <c r="D380" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E380" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F380" s="10">
+      <c r="E380" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F380" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A381" s="9" t="s">
+      <c r="A381" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B381" s="9" t="s">
+      <c r="B381" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C381" s="9" t="s">
+      <c r="C381" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D381" s="9" t="s">
+      <c r="D381" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E381" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F381" s="10">
+      <c r="E381" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F381" s="9">
         <v>46143</v>
       </c>
     </row>
@@ -8594,10 +8594,10 @@
       <c r="D382" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E382" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F382" s="8">
+      <c r="E382" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F382" s="7">
         <v>46143</v>
       </c>
     </row>
@@ -8614,70 +8614,70 @@
       <c r="D383" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E383" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F383" s="8">
+      <c r="E383" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F383" s="7">
         <v>46143</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A384" s="9" t="s">
+      <c r="A384" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B384" s="9" t="s">
+      <c r="B384" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C384" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D384" s="9" t="s">
+      <c r="C384" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D384" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E384" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F384" s="10">
+      <c r="E384" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F384" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A385" s="9" t="s">
+      <c r="A385" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B385" s="9" t="s">
+      <c r="B385" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C385" s="9" t="s">
+      <c r="C385" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D385" s="9" t="s">
+      <c r="D385" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E385" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F385" s="10">
+      <c r="E385" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F385" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" s="9" t="s">
+      <c r="A386" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B386" s="9" t="s">
+      <c r="B386" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C386" s="9" t="s">
+      <c r="C386" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D386" s="9" t="s">
+      <c r="D386" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E386" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F386" s="10">
+      <c r="E386" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F386" s="9">
         <v>46143</v>
       </c>
     </row>
@@ -8694,10 +8694,10 @@
       <c r="D387" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E387" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F387" s="8">
+      <c r="E387" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F387" s="7">
         <v>46143</v>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
       <c r="D388" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E388" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F388" s="8">
+      <c r="E388" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F388" s="7">
         <v>46143</v>
       </c>
     </row>
@@ -8734,71 +8734,211 @@
       <c r="D389" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E389" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F389" s="8">
+      <c r="E389" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F389" s="7">
         <v>46143</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" s="9" t="s">
+      <c r="A390" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B390" s="9" t="s">
+      <c r="B390" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C390" s="9" t="s">
+      <c r="C390" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D390" s="9" t="s">
+      <c r="D390" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E390" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F390" s="10">
+      <c r="E390" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F390" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A391" s="9" t="s">
+      <c r="A391" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B391" s="9" t="s">
+      <c r="B391" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C391" s="9" t="s">
+      <c r="C391" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D391" s="9" t="s">
+      <c r="D391" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E391" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F391" s="10">
+      <c r="E391" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F391" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A392" s="9" t="s">
+      <c r="A392" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B392" s="9" t="s">
+      <c r="B392" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C392" s="9" t="s">
+      <c r="C392" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D392" s="9" t="s">
+      <c r="D392" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E392" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F392" s="10">
+      <c r="E392" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F392" s="9">
         <v>46143</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E393" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F393" s="3">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E394" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F394" s="3">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E395" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F395" s="3">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A396" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E396" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F396" s="5">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A397" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E397" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F397" s="5">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E398" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F398" s="3">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E399" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F399" s="3">
+        <v>46172</v>
       </c>
     </row>
   </sheetData>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C7623C-9BAE-455B-BBDF-0B151D1F8DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="167">
   <si>
     <t>Wizards</t>
   </si>
@@ -525,6 +525,18 @@
   </si>
   <si>
     <t>Cache</t>
+  </si>
+  <si>
+    <t>Mana</t>
+  </si>
+  <si>
+    <t>FiReLEAGUE Buenos Aires 2026</t>
+  </si>
+  <si>
+    <t>MIBR Academy</t>
+  </si>
+  <si>
+    <t>AMKAL</t>
   </si>
 </sst>
 </file>
@@ -592,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -600,20 +612,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -634,7 +658,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -950,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:F399"/>
+  <dimension ref="A1:G423"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -958,7 +982,7 @@
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="39.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -982,22 +1006,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="6">
         <v>46023</v>
       </c>
     </row>
@@ -1017,27 +1041,27 @@
       <c r="E3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="7">
         <v>46023</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="6">
         <v>46023</v>
       </c>
     </row>
@@ -1057,27 +1081,27 @@
       <c r="E5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="7">
         <v>46023</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="6">
         <v>46023</v>
       </c>
     </row>
@@ -1097,27 +1121,27 @@
       <c r="E7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="7">
         <v>46023</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="6">
         <v>46023</v>
       </c>
     </row>
@@ -1137,27 +1161,27 @@
       <c r="E9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="7">
         <v>46023</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="6">
         <v>46024</v>
       </c>
     </row>
@@ -1177,27 +1201,27 @@
       <c r="E11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="7">
         <v>46024</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="6">
         <v>46024</v>
       </c>
     </row>
@@ -1217,27 +1241,27 @@
       <c r="E13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="7">
         <v>46024</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="E14" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="6">
         <v>46024</v>
       </c>
     </row>
@@ -1257,27 +1281,27 @@
       <c r="E15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="7">
         <v>46024</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F16" s="5">
+      <c r="E16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" s="6">
         <v>46024</v>
       </c>
     </row>
@@ -1297,27 +1321,27 @@
       <c r="E17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="7">
         <v>46024</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F18" s="5">
+      <c r="E18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="6">
         <v>46025</v>
       </c>
     </row>
@@ -1337,27 +1361,27 @@
       <c r="E19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="E20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="6">
         <v>46025</v>
       </c>
     </row>
@@ -1377,27 +1401,27 @@
       <c r="E21" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="E22" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="6">
         <v>46025</v>
       </c>
     </row>
@@ -1417,27 +1441,27 @@
       <c r="E23" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F24" s="5">
+      <c r="E24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="6">
         <v>46025</v>
       </c>
     </row>
@@ -1457,27 +1481,27 @@
       <c r="E25" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="E26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" s="6">
         <v>46026</v>
       </c>
     </row>
@@ -1497,27 +1521,27 @@
       <c r="E27" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="7">
         <v>46026</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F28" s="5">
+      <c r="E28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="6">
         <v>46026</v>
       </c>
     </row>
@@ -1537,27 +1561,27 @@
       <c r="E29" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="7">
         <v>46026</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="5">
+      <c r="E30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="6">
         <v>46026</v>
       </c>
     </row>
@@ -1577,27 +1601,27 @@
       <c r="E31" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="7">
         <v>46026</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="5">
+      <c r="E32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="6">
         <v>46026</v>
       </c>
     </row>
@@ -1617,27 +1641,27 @@
       <c r="E33" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="7">
         <v>46026</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="C34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="5">
+      <c r="E34" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="6">
         <v>46027</v>
       </c>
     </row>
@@ -1657,27 +1681,27 @@
       <c r="E35" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="7">
         <v>46027</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="E36" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" s="6">
         <v>46027</v>
       </c>
     </row>
@@ -1697,27 +1721,27 @@
       <c r="E37" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="7">
         <v>46027</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F38" s="5">
+      <c r="E38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="6">
         <v>46027</v>
       </c>
     </row>
@@ -1737,27 +1761,27 @@
       <c r="E39" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="7">
         <v>46027</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F40" s="5">
+      <c r="E40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F40" s="6">
         <v>46027</v>
       </c>
     </row>
@@ -1777,27 +1801,27 @@
       <c r="E41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="7">
         <v>46027</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="5">
+      <c r="E42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="6">
         <v>46028</v>
       </c>
     </row>
@@ -1817,27 +1841,27 @@
       <c r="E43" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="7">
         <v>46028</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F44" s="5">
+      <c r="E44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="6">
         <v>46028</v>
       </c>
     </row>
@@ -1857,27 +1881,27 @@
       <c r="E45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="7">
         <v>46028</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="C46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F46" s="5">
+      <c r="E46" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F46" s="6">
         <v>46028</v>
       </c>
     </row>
@@ -1897,27 +1921,27 @@
       <c r="E47" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="7">
         <v>46028</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F48" s="5">
+      <c r="E48" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F48" s="6">
         <v>46028</v>
       </c>
     </row>
@@ -1937,27 +1961,27 @@
       <c r="E49" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="7">
         <v>46028</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F50" s="5">
+      <c r="E50" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F50" s="6">
         <v>46029</v>
       </c>
     </row>
@@ -1977,27 +2001,27 @@
       <c r="E51" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="7">
         <v>46029</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F52" s="5">
+      <c r="E52" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F52" s="6">
         <v>46029</v>
       </c>
     </row>
@@ -2017,27 +2041,27 @@
       <c r="E53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="7">
         <v>46029</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="C54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F54" s="5">
+      <c r="E54" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F54" s="6">
         <v>46029</v>
       </c>
     </row>
@@ -2057,27 +2081,27 @@
       <c r="E55" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="7">
         <v>46029</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F56" s="5">
+      <c r="E56" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F56" s="6">
         <v>46029</v>
       </c>
     </row>
@@ -2097,47 +2121,47 @@
       <c r="E57" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="7">
         <v>46029</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F58" s="5">
+      <c r="E58" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F58" s="6">
         <v>46030</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="C59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F59" s="5">
+      <c r="E59" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F59" s="6">
         <v>46030</v>
       </c>
     </row>
@@ -2157,7 +2181,7 @@
       <c r="E60" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="7">
         <v>46030</v>
       </c>
     </row>
@@ -2177,7 +2201,7 @@
       <c r="E61" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="7">
         <v>46030</v>
       </c>
     </row>
@@ -2197,47 +2221,47 @@
       <c r="E62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="7">
         <v>46030</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="C63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F63" s="5">
+      <c r="E63" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F63" s="6">
         <v>46030</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="E64" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F64" s="6">
         <v>46030</v>
       </c>
     </row>
@@ -2257,7 +2281,7 @@
       <c r="E65" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="7">
         <v>46030</v>
       </c>
     </row>
@@ -2277,7 +2301,7 @@
       <c r="E66" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="7">
         <v>46030</v>
       </c>
     </row>
@@ -2297,67 +2321,67 @@
       <c r="E67" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="7">
         <v>46030</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="E68" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F68" s="6">
         <v>46031</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F69" s="5">
+      <c r="E69" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F69" s="6">
         <v>46031</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F70" s="5">
+      <c r="E70" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F70" s="6">
         <v>46031</v>
       </c>
     </row>
@@ -2377,7 +2401,7 @@
       <c r="E71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="7">
         <v>46031</v>
       </c>
     </row>
@@ -2397,7 +2421,7 @@
       <c r="E72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="7">
         <v>46031</v>
       </c>
     </row>
@@ -2417,47 +2441,47 @@
       <c r="E73" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="7">
         <v>46031</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F74" s="5">
+      <c r="E74" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F74" s="6">
         <v>46031</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F75" s="5">
+      <c r="E75" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F75" s="6">
         <v>46031</v>
       </c>
     </row>
@@ -2477,7 +2501,7 @@
       <c r="E76" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76" s="7">
         <v>46031</v>
       </c>
     </row>
@@ -2497,47 +2521,47 @@
       <c r="E77" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="7">
         <v>46031</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F78" s="5">
+      <c r="E78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F78" s="6">
         <v>46032</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="C79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F79" s="5">
+      <c r="E79" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" s="6">
         <v>46032</v>
       </c>
     </row>
@@ -2557,7 +2581,7 @@
       <c r="E80" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="7">
         <v>46032</v>
       </c>
     </row>
@@ -2577,47 +2601,47 @@
       <c r="E81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="7">
         <v>46032</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F82" s="5">
+      <c r="E82" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F82" s="6">
         <v>46032</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="C83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F83" s="5">
+      <c r="E83" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F83" s="6">
         <v>46032</v>
       </c>
     </row>
@@ -2637,7 +2661,7 @@
       <c r="E84" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="7">
         <v>46032</v>
       </c>
     </row>
@@ -2657,67 +2681,67 @@
       <c r="E85" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="7">
         <v>46032</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F86" s="5">
+      <c r="E86" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F86" s="6">
         <v>46033</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F87" s="5">
+      <c r="E87" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F87" s="6">
         <v>46033</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="C88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F88" s="5">
+      <c r="E88" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F88" s="6">
         <v>46033</v>
       </c>
     </row>
@@ -2737,7 +2761,7 @@
       <c r="E89" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="7">
         <v>46033</v>
       </c>
     </row>
@@ -2757,7 +2781,7 @@
       <c r="E90" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="7">
         <v>46033</v>
       </c>
     </row>
@@ -2777,47 +2801,47 @@
       <c r="E91" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="7">
         <v>46033</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F92" s="5">
+      <c r="E92" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F92" s="6">
         <v>46033</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E93" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F93" s="5">
+      <c r="E93" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F93" s="6">
         <v>46033</v>
       </c>
     </row>
@@ -2837,7 +2861,7 @@
       <c r="E94" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="7">
         <v>46033</v>
       </c>
     </row>
@@ -2857,7 +2881,7 @@
       <c r="E95" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="7">
         <v>46033</v>
       </c>
     </row>
@@ -2877,67 +2901,67 @@
       <c r="E96" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="7">
         <v>46033</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F97" s="5">
+      <c r="E97" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F97" s="6">
         <v>46033</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F98" s="5">
+      <c r="E98" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F98" s="6">
         <v>46033</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E99" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F99" s="6">
         <v>46033</v>
       </c>
     </row>
@@ -2957,7 +2981,7 @@
       <c r="E100" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="7">
         <v>46033</v>
       </c>
     </row>
@@ -2977,47 +3001,47 @@
       <c r="E101" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="7">
         <v>46033</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="4" t="s">
+      <c r="C102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F102" s="5">
+      <c r="E102" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F102" s="6">
         <v>46034</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E103" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F103" s="5">
+      <c r="E103" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F103" s="6">
         <v>46034</v>
       </c>
     </row>
@@ -3037,7 +3061,7 @@
       <c r="E104" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104" s="7">
         <v>46034</v>
       </c>
     </row>
@@ -3057,7 +3081,7 @@
       <c r="E105" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105" s="7">
         <v>46034</v>
       </c>
     </row>
@@ -3077,47 +3101,47 @@
       <c r="E106" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="7">
         <v>46034</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E107" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F107" s="5">
+      <c r="E107" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F107" s="6">
         <v>46034</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F108" s="5">
+      <c r="E108" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F108" s="6">
         <v>46034</v>
       </c>
     </row>
@@ -3137,7 +3161,7 @@
       <c r="E109" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="7">
         <v>46034</v>
       </c>
     </row>
@@ -3157,7 +3181,7 @@
       <c r="E110" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="7">
         <v>46034</v>
       </c>
     </row>
@@ -3177,47 +3201,47 @@
       <c r="E111" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="7">
         <v>46034</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F112" s="5">
+      <c r="E112" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F112" s="6">
         <v>46034</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="C113" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E113" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F113" s="5">
+      <c r="E113" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F113" s="6">
         <v>46034</v>
       </c>
     </row>
@@ -3237,7 +3261,7 @@
       <c r="E114" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="7">
         <v>46034</v>
       </c>
     </row>
@@ -3257,67 +3281,67 @@
       <c r="E115" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="7">
         <v>46034</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F116" s="5">
+      <c r="E116" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F116" s="6">
         <v>46035</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F117" s="5">
+      <c r="E117" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F117" s="6">
         <v>46035</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D118" s="4" t="s">
+      <c r="C118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F118" s="5">
+      <c r="E118" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F118" s="6">
         <v>46035</v>
       </c>
     </row>
@@ -3337,7 +3361,7 @@
       <c r="E119" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="7">
         <v>46035</v>
       </c>
     </row>
@@ -3357,47 +3381,47 @@
       <c r="E120" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="7">
         <v>46035</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="C121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F121" s="5">
+      <c r="E121" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F121" s="6">
         <v>46035</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E122" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F122" s="5">
+      <c r="E122" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F122" s="6">
         <v>46035</v>
       </c>
     </row>
@@ -3417,7 +3441,7 @@
       <c r="E123" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="7">
         <v>46035</v>
       </c>
     </row>
@@ -3437,47 +3461,47 @@
       <c r="E124" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="7">
         <v>46035</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D125" s="4" t="s">
+      <c r="C125" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E125" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F125" s="5">
+      <c r="E125" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F125" s="6">
         <v>46035</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F126" s="5">
+      <c r="E126" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F126" s="6">
         <v>46035</v>
       </c>
     </row>
@@ -3497,7 +3521,7 @@
       <c r="E127" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="7">
         <v>46036</v>
       </c>
     </row>
@@ -3517,7 +3541,7 @@
       <c r="E128" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="7">
         <v>46036</v>
       </c>
     </row>
@@ -3537,47 +3561,47 @@
       <c r="E129" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="7">
         <v>46036</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E130" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F130" s="5">
+      <c r="E130" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F130" s="6">
         <v>46036</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C131" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D131" s="4" t="s">
+      <c r="C131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F131" s="5">
+      <c r="E131" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F131" s="6">
         <v>46036</v>
       </c>
     </row>
@@ -3597,7 +3621,7 @@
       <c r="E132" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="7">
         <v>46036</v>
       </c>
     </row>
@@ -3617,87 +3641,87 @@
       <c r="E133" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="7">
         <v>46036</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E134" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F134" s="5">
+      <c r="E134" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F134" s="6">
         <v>46036</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E135" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F135" s="5">
+      <c r="E135" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F135" s="6">
         <v>46036</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="D136" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E136" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F136" s="5">
+      <c r="E136" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F136" s="6">
         <v>46036</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F137" s="5">
+      <c r="E137" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F137" s="6">
         <v>46036</v>
       </c>
     </row>
@@ -3717,7 +3741,7 @@
       <c r="E138" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="7">
         <v>46036</v>
       </c>
     </row>
@@ -3737,47 +3761,47 @@
       <c r="E139" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139" s="7">
         <v>46036</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E140" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F140" s="5">
+      <c r="E140" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F140" s="6">
         <v>46037</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E141" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F141" s="5">
+      <c r="E141" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F141" s="6">
         <v>46037</v>
       </c>
     </row>
@@ -3797,7 +3821,7 @@
       <c r="E142" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="7">
         <v>46037</v>
       </c>
     </row>
@@ -3817,67 +3841,67 @@
       <c r="E143" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="7">
         <v>46037</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F144" s="5">
+      <c r="E144" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F144" s="6">
         <v>46037</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E145" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F145" s="5">
+      <c r="E145" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F145" s="6">
         <v>46037</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146" s="4" t="s">
+      <c r="C146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E146" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F146" s="5">
+      <c r="E146" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F146" s="6">
         <v>46037</v>
       </c>
     </row>
@@ -3897,7 +3921,7 @@
       <c r="E147" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="7">
         <v>46037</v>
       </c>
     </row>
@@ -3917,67 +3941,67 @@
       <c r="E148" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="7">
         <v>46037</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D149" s="4" t="s">
+      <c r="C149" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E149" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F149" s="5">
+      <c r="E149" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F149" s="6">
         <v>46038</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="D150" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E150" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F150" s="5">
+      <c r="E150" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F150" s="6">
         <v>46038</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E151" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F151" s="5">
+      <c r="E151" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F151" s="6">
         <v>46038</v>
       </c>
     </row>
@@ -3997,7 +4021,7 @@
       <c r="E152" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152" s="7">
         <v>46038</v>
       </c>
     </row>
@@ -4017,7 +4041,7 @@
       <c r="E153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153" s="7">
         <v>46038</v>
       </c>
     </row>
@@ -4037,52 +4061,52 @@
       <c r="E154" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154" s="7">
         <v>46038</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E155" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F155" s="5">
+      <c r="E155" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F155" s="6">
         <v>46038</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E156" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F156" s="5">
+      <c r="E156" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F156" s="6">
         <v>46038</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -4097,7 +4121,7 @@
       <c r="E157" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157" s="7">
         <v>46038</v>
       </c>
     </row>
@@ -4117,7 +4141,7 @@
       <c r="E158" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158" s="7">
         <v>46038</v>
       </c>
     </row>
@@ -4137,47 +4161,47 @@
       <c r="E159" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159" s="7">
         <v>46038</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="D160" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E160" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F160" s="5">
+      <c r="E160" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F160" s="6">
         <v>46038</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="D161" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E161" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F161" s="5">
+      <c r="E161" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F161" s="6">
         <v>46038</v>
       </c>
     </row>
@@ -4197,7 +4221,7 @@
       <c r="E162" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162" s="7">
         <v>46039</v>
       </c>
     </row>
@@ -4217,7 +4241,7 @@
       <c r="E163" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163" s="7">
         <v>46039</v>
       </c>
     </row>
@@ -4237,47 +4261,47 @@
       <c r="E164" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="7">
         <v>46039</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E165" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F165" s="5">
+      <c r="E165" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F165" s="6">
         <v>46039</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E166" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F166" s="5">
+      <c r="E166" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F166" s="6">
         <v>46039</v>
       </c>
     </row>
@@ -4297,7 +4321,7 @@
       <c r="E167" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167" s="7">
         <v>46040</v>
       </c>
     </row>
@@ -4317,67 +4341,67 @@
       <c r="E168" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F168" s="3">
+      <c r="F168" s="7">
         <v>46040</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="D169" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E169" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F169" s="5">
+      <c r="E169" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F169" s="6">
         <v>46040</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C170" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D170" s="4" t="s">
+      <c r="C170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E170" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F170" s="5">
+      <c r="E170" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F170" s="6">
         <v>46040</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="D171" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E171" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F171" s="5">
+      <c r="E171" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F171" s="6">
         <v>46040</v>
       </c>
     </row>
@@ -4397,7 +4421,7 @@
       <c r="E172" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F172" s="3">
+      <c r="F172" s="7">
         <v>46041</v>
       </c>
     </row>
@@ -4417,7 +4441,7 @@
       <c r="E173" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F173" s="3">
+      <c r="F173" s="7">
         <v>46041</v>
       </c>
     </row>
@@ -4437,47 +4461,47 @@
       <c r="E174" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F174" s="3">
+      <c r="F174" s="7">
         <v>46041</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E175" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F175" s="5">
+      <c r="E175" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F175" s="6">
         <v>46041</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E176" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F176" s="5">
+      <c r="E176" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F176" s="6">
         <v>46041</v>
       </c>
     </row>
@@ -4497,7 +4521,7 @@
       <c r="E177" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F177" s="7">
         <v>46041</v>
       </c>
     </row>
@@ -4517,7 +4541,7 @@
       <c r="E178" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="7">
         <v>46041</v>
       </c>
     </row>
@@ -4537,47 +4561,47 @@
       <c r="E179" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F179" s="7">
         <v>46041</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C180" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D180" s="4" t="s">
+      <c r="C180" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E180" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F180" s="5">
+      <c r="E180" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F180" s="6">
         <v>46041</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E181" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F181" s="5">
+      <c r="E181" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F181" s="6">
         <v>46041</v>
       </c>
     </row>
@@ -4597,7 +4621,7 @@
       <c r="E182" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F182" s="3">
+      <c r="F182" s="7">
         <v>46042</v>
       </c>
     </row>
@@ -4617,7 +4641,7 @@
       <c r="E183" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183" s="7">
         <v>46042</v>
       </c>
     </row>
@@ -4637,47 +4661,47 @@
       <c r="E184" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F184" s="3">
+      <c r="F184" s="7">
         <v>46042</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D185" s="4" t="s">
+      <c r="D185" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E185" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F185" s="5">
+      <c r="E185" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F185" s="6">
         <v>46042</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D186" s="4" t="s">
+      <c r="D186" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E186" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F186" s="5">
+      <c r="E186" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F186" s="6">
         <v>46042</v>
       </c>
     </row>
@@ -4697,7 +4721,7 @@
       <c r="E187" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187" s="7">
         <v>46042</v>
       </c>
     </row>
@@ -4717,7 +4741,7 @@
       <c r="E188" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F188" s="3">
+      <c r="F188" s="7">
         <v>46042</v>
       </c>
     </row>
@@ -4737,47 +4761,47 @@
       <c r="E189" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189" s="7">
         <v>46042</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C190" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D190" s="4" t="s">
+      <c r="C190" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E190" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F190" s="5">
+      <c r="E190" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F190" s="6">
         <v>46042</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D191" s="4" t="s">
+      <c r="D191" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E191" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F191" s="5">
+      <c r="E191" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F191" s="6">
         <v>46042</v>
       </c>
     </row>
@@ -4797,7 +4821,7 @@
       <c r="E192" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F192" s="3">
+      <c r="F192" s="7">
         <v>46043</v>
       </c>
     </row>
@@ -4817,67 +4841,67 @@
       <c r="E193" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193" s="7">
         <v>46043</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D194" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E194" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F194" s="5">
+      <c r="E194" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F194" s="6">
         <v>46043</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
+      <c r="A195" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D195" s="4" t="s">
+      <c r="D195" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E195" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F195" s="5">
+      <c r="E195" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F195" s="6">
         <v>46043</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D196" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E196" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F196" s="5">
+      <c r="E196" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F196" s="6">
         <v>46043</v>
       </c>
     </row>
@@ -4897,7 +4921,7 @@
       <c r="E197" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F197" s="7">
         <v>46043</v>
       </c>
     </row>
@@ -4917,7 +4941,7 @@
       <c r="E198" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F198" s="3">
+      <c r="F198" s="7">
         <v>46043</v>
       </c>
     </row>
@@ -4937,67 +4961,67 @@
       <c r="E199" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F199" s="3">
+      <c r="F199" s="7">
         <v>46043</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
+      <c r="A200" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D200" s="4" t="s">
+      <c r="D200" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E200" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F200" s="5">
+      <c r="E200" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F200" s="6">
         <v>46043</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="s">
+      <c r="A201" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="D201" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E201" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F201" s="5">
+      <c r="E201" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F201" s="6">
         <v>46043</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D202" s="4" t="s">
+      <c r="D202" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E202" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F202" s="5">
+      <c r="E202" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F202" s="6">
         <v>46043</v>
       </c>
     </row>
@@ -5017,7 +5041,7 @@
       <c r="E203" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F203" s="3">
+      <c r="F203" s="7">
         <v>46044</v>
       </c>
     </row>
@@ -5037,7 +5061,7 @@
       <c r="E204" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F204" s="3">
+      <c r="F204" s="7">
         <v>46044</v>
       </c>
     </row>
@@ -5057,47 +5081,47 @@
       <c r="E205" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F205" s="3">
+      <c r="F205" s="7">
         <v>46044</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D206" s="4" t="s">
+      <c r="D206" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E206" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F206" s="5">
+      <c r="E206" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F206" s="6">
         <v>46044</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D207" s="4" t="s">
+      <c r="D207" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E207" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F207" s="5">
+      <c r="E207" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F207" s="6">
         <v>46044</v>
       </c>
     </row>
@@ -5117,7 +5141,7 @@
       <c r="E208" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F208" s="3">
+      <c r="F208" s="7">
         <v>46044</v>
       </c>
     </row>
@@ -5137,7 +5161,7 @@
       <c r="E209" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F209" s="3">
+      <c r="F209" s="7">
         <v>46044</v>
       </c>
     </row>
@@ -5157,47 +5181,47 @@
       <c r="E210" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F210" s="3">
+      <c r="F210" s="7">
         <v>46044</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E211" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F211" s="5">
+      <c r="E211" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F211" s="6">
         <v>46044</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E212" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F212" s="5">
+      <c r="E212" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F212" s="6">
         <v>46044</v>
       </c>
     </row>
@@ -5217,7 +5241,7 @@
       <c r="E213" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F213" s="3">
+      <c r="F213" s="7">
         <v>46044</v>
       </c>
     </row>
@@ -5237,47 +5261,47 @@
       <c r="E214" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F214" s="3">
+      <c r="F214" s="7">
         <v>46044</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D215" s="4" t="s">
+      <c r="D215" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E215" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F215" s="5">
+      <c r="E215" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F215" s="6">
         <v>46044</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D216" s="4" t="s">
+      <c r="D216" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E216" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F216" s="5">
+      <c r="E216" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F216" s="6">
         <v>46044</v>
       </c>
     </row>
@@ -5297,7 +5321,7 @@
       <c r="E217" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F217" s="3">
+      <c r="F217" s="7">
         <v>46045</v>
       </c>
     </row>
@@ -5317,7 +5341,7 @@
       <c r="E218" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F218" s="3">
+      <c r="F218" s="7">
         <v>46045</v>
       </c>
     </row>
@@ -5337,47 +5361,47 @@
       <c r="E219" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F219" s="3">
+      <c r="F219" s="7">
         <v>46045</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D220" s="4" t="s">
+      <c r="D220" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E220" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F220" s="5">
+      <c r="E220" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F220" s="6">
         <v>46045</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="4" t="s">
+      <c r="A221" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D221" s="4" t="s">
+      <c r="D221" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E221" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F221" s="5">
+      <c r="E221" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F221" s="6">
         <v>46045</v>
       </c>
     </row>
@@ -5397,7 +5421,7 @@
       <c r="E222" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F222" s="3">
+      <c r="F222" s="7">
         <v>46045</v>
       </c>
     </row>
@@ -5417,7 +5441,7 @@
       <c r="E223" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F223" s="3">
+      <c r="F223" s="7">
         <v>46045</v>
       </c>
     </row>
@@ -5437,47 +5461,47 @@
       <c r="E224" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F224" s="3">
+      <c r="F224" s="7">
         <v>46045</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C225" s="4" t="s">
+      <c r="C225" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D225" s="4" t="s">
+      <c r="D225" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E225" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F225" s="5">
+      <c r="E225" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F225" s="6">
         <v>46045</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C226" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D226" s="4" t="s">
+      <c r="D226" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E226" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F226" s="5">
+      <c r="E226" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F226" s="6">
         <v>46045</v>
       </c>
     </row>
@@ -5497,7 +5521,7 @@
       <c r="E227" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F227" s="3">
+      <c r="F227" s="7">
         <v>46046</v>
       </c>
     </row>
@@ -5517,47 +5541,47 @@
       <c r="E228" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F228" s="3">
+      <c r="F228" s="7">
         <v>46046</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" s="4" t="s">
+      <c r="A229" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C229" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D229" s="4" t="s">
+      <c r="C229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D229" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E229" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F229" s="5">
+      <c r="E229" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F229" s="6">
         <v>46046</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C230" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D230" s="4" t="s">
+      <c r="D230" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E230" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F230" s="5">
+      <c r="E230" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F230" s="6">
         <v>46046</v>
       </c>
     </row>
@@ -5577,7 +5601,7 @@
       <c r="E231" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F231" s="3">
+      <c r="F231" s="7">
         <v>46046</v>
       </c>
     </row>
@@ -5597,67 +5621,67 @@
       <c r="E232" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F232" s="3">
+      <c r="F232" s="7">
         <v>46046</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="4" t="s">
+      <c r="A233" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C233" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D233" s="4" t="s">
+      <c r="C233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E233" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F233" s="5">
+      <c r="E233" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F233" s="6">
         <v>46046</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="4" t="s">
+      <c r="A234" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C234" s="4" t="s">
+      <c r="C234" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D234" s="4" t="s">
+      <c r="D234" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E234" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F234" s="5">
+      <c r="E234" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F234" s="6">
         <v>46046</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="4" t="s">
+      <c r="A235" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="C235" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D235" s="4" t="s">
+      <c r="D235" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E235" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F235" s="5">
+      <c r="E235" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F235" s="6">
         <v>46046</v>
       </c>
     </row>
@@ -5677,7 +5701,7 @@
       <c r="E236" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F236" s="3">
+      <c r="F236" s="7">
         <v>46046</v>
       </c>
     </row>
@@ -5697,67 +5721,67 @@
       <c r="E237" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F237" s="3">
+      <c r="F237" s="7">
         <v>46046</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C238" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D238" s="4" t="s">
+      <c r="D238" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E238" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F238" s="5">
+      <c r="E238" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F238" s="6">
         <v>46046</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="4" t="s">
+      <c r="A239" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="C239" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="D239" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E239" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F239" s="5">
+      <c r="E239" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F239" s="6">
         <v>46046</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" s="4" t="s">
+      <c r="A240" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C240" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D240" s="4" t="s">
+      <c r="C240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E240" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F240" s="5">
+      <c r="E240" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F240" s="6">
         <v>46046</v>
       </c>
     </row>
@@ -5777,7 +5801,7 @@
       <c r="E241" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F241" s="3">
+      <c r="F241" s="7">
         <v>46047</v>
       </c>
     </row>
@@ -5797,67 +5821,67 @@
       <c r="E242" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F242" s="3">
+      <c r="F242" s="7">
         <v>46047</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="4" t="s">
+      <c r="A243" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B243" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D243" s="4" t="s">
+      <c r="D243" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E243" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F243" s="5">
+      <c r="E243" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F243" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="4" t="s">
+      <c r="A244" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C244" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="D244" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E244" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F244" s="5">
+      <c r="E244" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F244" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="4" t="s">
+      <c r="A245" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C245" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D245" s="4" t="s">
+      <c r="C245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E245" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F245" s="5">
+      <c r="E245" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F245" s="6">
         <v>46047</v>
       </c>
     </row>
@@ -5877,7 +5901,7 @@
       <c r="E246" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F246" s="3">
+      <c r="F246" s="7">
         <v>46047</v>
       </c>
     </row>
@@ -5897,7 +5921,7 @@
       <c r="E247" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F247" s="3">
+      <c r="F247" s="7">
         <v>46047</v>
       </c>
     </row>
@@ -5917,67 +5941,67 @@
       <c r="E248" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F248" s="3">
+      <c r="F248" s="7">
         <v>46047</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" s="4" t="s">
+      <c r="A249" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D249" s="4" t="s">
+      <c r="D249" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E249" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F249" s="5">
+      <c r="E249" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F249" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" s="4" t="s">
+      <c r="A250" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D250" s="4" t="s">
+      <c r="D250" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E250" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F250" s="5">
+      <c r="E250" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F250" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" s="4" t="s">
+      <c r="A251" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C251" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D251" s="4" t="s">
+      <c r="C251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D251" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E251" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F251" s="5">
+      <c r="E251" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F251" s="6">
         <v>46047</v>
       </c>
     </row>
@@ -5997,7 +6021,7 @@
       <c r="E252" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F252" s="3">
+      <c r="F252" s="7">
         <v>46047</v>
       </c>
     </row>
@@ -6017,7 +6041,7 @@
       <c r="E253" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F253" s="3">
+      <c r="F253" s="7">
         <v>46047</v>
       </c>
     </row>
@@ -6037,67 +6061,67 @@
       <c r="E254" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F254" s="3">
+      <c r="F254" s="7">
         <v>46047</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B255" s="4" t="s">
+      <c r="B255" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C255" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D255" s="4" t="s">
+      <c r="C255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D255" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E255" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F255" s="5">
+      <c r="E255" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F255" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="4" t="s">
+      <c r="A256" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C256" s="4" t="s">
+      <c r="C256" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="D256" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E256" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F256" s="5">
+      <c r="E256" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F256" s="6">
         <v>46047</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" s="4" t="s">
+      <c r="A257" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="D257" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E257" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F257" s="5">
+      <c r="E257" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F257" s="6">
         <v>46047</v>
       </c>
     </row>
@@ -6117,7 +6141,7 @@
       <c r="E258" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F258" s="3">
+      <c r="F258" s="7">
         <v>46048</v>
       </c>
     </row>
@@ -6137,47 +6161,47 @@
       <c r="E259" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F259" s="3">
+      <c r="F259" s="7">
         <v>46048</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" s="4" t="s">
+      <c r="A260" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D260" s="4" t="s">
+      <c r="D260" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E260" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F260" s="5">
+      <c r="E260" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F260" s="6">
         <v>46048</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" s="4" t="s">
+      <c r="A261" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B261" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D261" s="4" t="s">
+      <c r="D261" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E261" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F261" s="5">
+      <c r="E261" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F261" s="6">
         <v>46048</v>
       </c>
     </row>
@@ -6197,7 +6221,7 @@
       <c r="E262" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F262" s="3">
+      <c r="F262" s="7">
         <v>46049</v>
       </c>
     </row>
@@ -6217,47 +6241,47 @@
       <c r="E263" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F263" s="3">
+      <c r="F263" s="7">
         <v>46049</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" s="4" t="s">
+      <c r="A264" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D264" s="4" t="s">
+      <c r="D264" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E264" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F264" s="5">
+      <c r="E264" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F264" s="6">
         <v>46049</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" s="4" t="s">
+      <c r="A265" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B265" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="D265" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E265" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F265" s="5">
+      <c r="E265" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F265" s="6">
         <v>46049</v>
       </c>
     </row>
@@ -6277,7 +6301,7 @@
       <c r="E266" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F266" s="3">
+      <c r="F266" s="7">
         <v>46049</v>
       </c>
     </row>
@@ -6297,7 +6321,7 @@
       <c r="E267" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F267" s="3">
+      <c r="F267" s="7">
         <v>46049</v>
       </c>
     </row>
@@ -6317,47 +6341,47 @@
       <c r="E268" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F268" s="3">
+      <c r="F268" s="7">
         <v>46049</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" s="4" t="s">
+      <c r="A269" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B269" s="4" t="s">
+      <c r="B269" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D269" s="4" t="s">
+      <c r="D269" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E269" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F269" s="5">
+      <c r="E269" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F269" s="6">
         <v>46049</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" s="4" t="s">
+      <c r="A270" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="D270" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E270" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F270" s="5">
+      <c r="E270" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F270" s="6">
         <v>46049</v>
       </c>
     </row>
@@ -6377,7 +6401,7 @@
       <c r="E271" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F271" s="3">
+      <c r="F271" s="7">
         <v>46050</v>
       </c>
     </row>
@@ -6397,7 +6421,7 @@
       <c r="E272" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F272" s="3">
+      <c r="F272" s="7">
         <v>46050</v>
       </c>
     </row>
@@ -6417,67 +6441,67 @@
       <c r="E273" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F273" s="3">
+      <c r="F273" s="7">
         <v>46050</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" s="4" t="s">
+      <c r="A274" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C274" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D274" s="4" t="s">
+      <c r="C274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D274" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E274" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F274" s="5">
+      <c r="E274" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F274" s="6">
         <v>46050</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" s="4" t="s">
+      <c r="A275" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C275" s="4" t="s">
+      <c r="C275" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D275" s="4" t="s">
+      <c r="D275" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E275" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F275" s="5">
+      <c r="E275" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F275" s="6">
         <v>46050</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="4" t="s">
+      <c r="A276" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C276" s="4" t="s">
+      <c r="C276" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D276" s="4" t="s">
+      <c r="D276" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E276" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F276" s="5">
+      <c r="E276" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F276" s="6">
         <v>46050</v>
       </c>
     </row>
@@ -6497,7 +6521,7 @@
       <c r="E277" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F277" s="3">
+      <c r="F277" s="7">
         <v>46050</v>
       </c>
     </row>
@@ -6517,47 +6541,47 @@
       <c r="E278" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F278" s="3">
+      <c r="F278" s="7">
         <v>46050</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="4" t="s">
+      <c r="A279" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C279" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D279" s="4" t="s">
+      <c r="C279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D279" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E279" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F279" s="5">
+      <c r="E279" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F279" s="6">
         <v>46051</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B280" s="4" t="s">
+      <c r="B280" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="C280" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D280" s="4" t="s">
+      <c r="D280" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E280" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F280" s="5">
+      <c r="E280" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F280" s="6">
         <v>46051</v>
       </c>
     </row>
@@ -6577,7 +6601,7 @@
       <c r="E281" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F281" s="3">
+      <c r="F281" s="7">
         <v>46051</v>
       </c>
     </row>
@@ -6597,67 +6621,67 @@
       <c r="E282" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F282" s="3">
+      <c r="F282" s="7">
         <v>46051</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" s="4" t="s">
+      <c r="A283" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="C283" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D283" s="4" t="s">
+      <c r="D283" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E283" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F283" s="5">
+      <c r="E283" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F283" s="6">
         <v>46051</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" s="4" t="s">
+      <c r="A284" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B284" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="D284" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E284" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F284" s="5">
+      <c r="E284" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F284" s="6">
         <v>46051</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285" s="4" t="s">
+      <c r="A285" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C285" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D285" s="4" t="s">
+      <c r="C285" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D285" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E285" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F285" s="5">
+      <c r="E285" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F285" s="6">
         <v>46051</v>
       </c>
     </row>
@@ -6677,7 +6701,7 @@
       <c r="E286" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F286" s="3">
+      <c r="F286" s="7">
         <v>46051</v>
       </c>
     </row>
@@ -6697,7 +6721,7 @@
       <c r="E287" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F287" s="3">
+      <c r="F287" s="7">
         <v>46051</v>
       </c>
     </row>
@@ -6717,47 +6741,47 @@
       <c r="E288" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F288" s="3">
+      <c r="F288" s="7">
         <v>46051</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289" s="4" t="s">
+      <c r="A289" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C289" s="4" t="s">
+      <c r="C289" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D289" s="4" t="s">
+      <c r="D289" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E289" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F289" s="5">
+      <c r="E289" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F289" s="6">
         <v>46052</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290" s="4" t="s">
+      <c r="A290" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C290" s="4" t="s">
+      <c r="C290" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D290" s="4" t="s">
+      <c r="D290" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E290" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F290" s="5">
+      <c r="E290" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F290" s="6">
         <v>46052</v>
       </c>
     </row>
@@ -6777,7 +6801,7 @@
       <c r="E291" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F291" s="3">
+      <c r="F291" s="7">
         <v>46052</v>
       </c>
     </row>
@@ -6797,7 +6821,7 @@
       <c r="E292" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F292" s="3">
+      <c r="F292" s="7">
         <v>46052</v>
       </c>
     </row>
@@ -6817,27 +6841,27 @@
       <c r="E293" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F293" s="3">
+      <c r="F293" s="7">
         <v>46052</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294" s="4" t="s">
+      <c r="A294" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C294" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D294" s="4" t="s">
+      <c r="C294" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D294" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E294" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F294" s="5">
+      <c r="E294" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F294" s="6">
         <v>46053</v>
       </c>
     </row>
@@ -6857,27 +6881,27 @@
       <c r="E295" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F295" s="3">
+      <c r="F295" s="7">
         <v>46053</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C296" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D296" s="4" t="s">
+      <c r="C296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D296" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E296" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F296" s="5">
+      <c r="E296" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F296" s="6">
         <v>46053</v>
       </c>
     </row>
@@ -6897,27 +6921,27 @@
       <c r="E297" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F297" s="3">
+      <c r="F297" s="7">
         <v>46053</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298" s="4" t="s">
+      <c r="A298" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C298" s="4" t="s">
+      <c r="C298" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D298" s="4" t="s">
+      <c r="D298" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E298" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F298" s="5">
+      <c r="E298" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F298" s="6">
         <v>46053</v>
       </c>
     </row>
@@ -6937,27 +6961,27 @@
       <c r="E299" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F299" s="3">
+      <c r="F299" s="7">
         <v>46053</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" s="4" t="s">
+      <c r="A300" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C300" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D300" s="4" t="s">
+      <c r="C300" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D300" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E300" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F300" s="5">
+      <c r="E300" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F300" s="6">
         <v>46053</v>
       </c>
     </row>
@@ -6977,27 +7001,27 @@
       <c r="E301" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F301" s="3">
+      <c r="F301" s="7">
         <v>46053</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="4" t="s">
+      <c r="A302" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="C302" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D302" s="4" t="s">
+      <c r="D302" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E302" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F302" s="5">
+      <c r="E302" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F302" s="6">
         <v>46054</v>
       </c>
     </row>
@@ -7017,27 +7041,27 @@
       <c r="E303" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F303" s="3">
+      <c r="F303" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B304" s="4" t="s">
+      <c r="B304" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C304" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D304" s="4" t="s">
+      <c r="C304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D304" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E304" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F304" s="5">
+      <c r="E304" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F304" s="6">
         <v>46054</v>
       </c>
     </row>
@@ -7057,27 +7081,27 @@
       <c r="E305" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F305" s="3">
+      <c r="F305" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" s="4" t="s">
+      <c r="A306" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="B306" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C306" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D306" s="4" t="s">
+      <c r="C306" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D306" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E306" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F306" s="5">
+      <c r="E306" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F306" s="6">
         <v>46054</v>
       </c>
     </row>
@@ -7097,27 +7121,27 @@
       <c r="E307" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F307" s="3">
+      <c r="F307" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" s="4" t="s">
+      <c r="A308" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B308" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C308" s="4" t="s">
+      <c r="C308" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="D308" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E308" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F308" s="5">
+      <c r="E308" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F308" s="6">
         <v>46054</v>
       </c>
     </row>
@@ -7137,47 +7161,47 @@
       <c r="E309" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F309" s="3">
+      <c r="F309" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A310" s="4" t="s">
+      <c r="A310" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C310" s="4" t="s">
+      <c r="C310" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D310" s="4" t="s">
+      <c r="D310" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E310" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F310" s="5">
+      <c r="E310" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F310" s="6">
         <v>46055</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
+      <c r="A311" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B311" s="4" t="s">
+      <c r="B311" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C311" s="4" t="s">
+      <c r="C311" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D311" s="4" t="s">
+      <c r="D311" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E311" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F311" s="5">
+      <c r="E311" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F311" s="6">
         <v>46055</v>
       </c>
     </row>
@@ -7197,7 +7221,7 @@
       <c r="E312" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F312" s="3">
+      <c r="F312" s="7">
         <v>46055</v>
       </c>
     </row>
@@ -7217,7 +7241,7 @@
       <c r="E313" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F313" s="3">
+      <c r="F313" s="7">
         <v>46055</v>
       </c>
     </row>
@@ -7237,27 +7261,27 @@
       <c r="E314" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F314" s="3">
+      <c r="F314" s="7">
         <v>46055</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" s="4" t="s">
+      <c r="A315" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B315" s="4" t="s">
+      <c r="B315" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C315" s="4" t="s">
+      <c r="C315" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D315" s="4" t="s">
+      <c r="D315" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E315" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F315" s="5">
+      <c r="E315" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F315" s="6">
         <v>46055</v>
       </c>
     </row>
@@ -7277,27 +7301,27 @@
       <c r="E316" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F316" s="3">
+      <c r="F316" s="7">
         <v>46055</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" s="4" t="s">
+      <c r="A317" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B317" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C317" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D317" s="4" t="s">
+      <c r="C317" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D317" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E317" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F317" s="5">
+      <c r="E317" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F317" s="6">
         <v>46055</v>
       </c>
     </row>
@@ -7317,47 +7341,47 @@
       <c r="E318" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F318" s="3">
+      <c r="F318" s="7">
         <v>46055</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" s="4" t="s">
+      <c r="A319" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="B319" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C319" s="4" t="s">
+      <c r="C319" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D319" s="4" t="s">
+      <c r="D319" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E319" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F319" s="5">
+      <c r="E319" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F319" s="6">
         <v>46056</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="B320" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C320" s="4" t="s">
+      <c r="C320" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D320" s="4" t="s">
+      <c r="D320" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E320" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F320" s="5">
+      <c r="E320" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F320" s="6">
         <v>46056</v>
       </c>
     </row>
@@ -7377,7 +7401,7 @@
       <c r="E321" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F321" s="3">
+      <c r="F321" s="7">
         <v>46056</v>
       </c>
     </row>
@@ -7397,7 +7421,7 @@
       <c r="E322" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F322" s="3">
+      <c r="F322" s="7">
         <v>46056</v>
       </c>
     </row>
@@ -7417,67 +7441,67 @@
       <c r="E323" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F323" s="3">
+      <c r="F323" s="7">
         <v>46056</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A324" s="4" t="s">
+      <c r="A324" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B324" s="4" t="s">
+      <c r="B324" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C324" s="4" t="s">
+      <c r="C324" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D324" s="4" t="s">
+      <c r="D324" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E324" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F324" s="5">
+      <c r="E324" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F324" s="6">
         <v>46057</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A325" s="4" t="s">
+      <c r="A325" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B325" s="4" t="s">
+      <c r="B325" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C325" s="4" t="s">
+      <c r="C325" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D325" s="4" t="s">
+      <c r="D325" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E325" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F325" s="5">
+      <c r="E325" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F325" s="6">
         <v>46057</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A326" s="4" t="s">
+      <c r="A326" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="B326" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C326" s="4" t="s">
+      <c r="C326" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D326" s="4" t="s">
+      <c r="D326" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E326" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F326" s="5">
+      <c r="E326" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F326" s="6">
         <v>46057</v>
       </c>
     </row>
@@ -7497,7 +7521,7 @@
       <c r="E327" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F327" s="3">
+      <c r="F327" s="7">
         <v>46057</v>
       </c>
     </row>
@@ -7517,47 +7541,47 @@
       <c r="E328" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F328" s="3">
+      <c r="F328" s="7">
         <v>46057</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="B329" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C329" s="4" t="s">
+      <c r="C329" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D329" s="4" t="s">
+      <c r="D329" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E329" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F329" s="5">
+      <c r="E329" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F329" s="6">
         <v>46057</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A330" s="4" t="s">
+      <c r="A330" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B330" s="4" t="s">
+      <c r="B330" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C330" s="4" t="s">
+      <c r="C330" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D330" s="4" t="s">
+      <c r="D330" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E330" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F330" s="5">
+      <c r="E330" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F330" s="6">
         <v>46057</v>
       </c>
     </row>
@@ -7577,7 +7601,7 @@
       <c r="E331" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F331" s="3">
+      <c r="F331" s="7">
         <v>46058</v>
       </c>
     </row>
@@ -7597,7 +7621,7 @@
       <c r="E332" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F332" s="3">
+      <c r="F332" s="7">
         <v>46058</v>
       </c>
     </row>
@@ -7617,47 +7641,47 @@
       <c r="E333" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F333" s="3">
+      <c r="F333" s="7">
         <v>46058</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" s="4" t="s">
+      <c r="A334" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B334" s="4" t="s">
+      <c r="B334" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C334" s="4" t="s">
+      <c r="C334" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D334" s="4" t="s">
+      <c r="D334" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E334" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F334" s="5">
+      <c r="E334" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F334" s="6">
         <v>46058</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" s="4" t="s">
+      <c r="A335" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B335" s="4" t="s">
+      <c r="B335" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C335" s="4" t="s">
+      <c r="C335" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D335" s="4" t="s">
+      <c r="D335" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E335" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F335" s="5">
+      <c r="E335" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F335" s="6">
         <v>46058</v>
       </c>
     </row>
@@ -7677,7 +7701,7 @@
       <c r="E336" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F336" s="3">
+      <c r="F336" s="7">
         <v>46058</v>
       </c>
     </row>
@@ -7697,7 +7721,7 @@
       <c r="E337" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F337" s="3">
+      <c r="F337" s="7">
         <v>46058</v>
       </c>
     </row>
@@ -7717,67 +7741,67 @@
       <c r="E338" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F338" s="3">
+      <c r="F338" s="7">
         <v>46058</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A339" s="4" t="s">
+      <c r="A339" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B339" s="4" t="s">
+      <c r="B339" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C339" s="4" t="s">
+      <c r="C339" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D339" s="4" t="s">
+      <c r="D339" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E339" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F339" s="5">
+      <c r="E339" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F339" s="6">
         <v>46059</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A340" s="4" t="s">
+      <c r="A340" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B340" s="4" t="s">
+      <c r="B340" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C340" s="4" t="s">
+      <c r="C340" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D340" s="4" t="s">
+      <c r="D340" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E340" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F340" s="5">
+      <c r="E340" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F340" s="6">
         <v>46059</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="B341" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C341" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D341" s="4" t="s">
+      <c r="C341" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D341" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E341" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F341" s="5">
+      <c r="E341" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F341" s="6">
         <v>46059</v>
       </c>
     </row>
@@ -7797,7 +7821,7 @@
       <c r="E342" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F342" s="3">
+      <c r="F342" s="7">
         <v>46059</v>
       </c>
     </row>
@@ -7817,67 +7841,67 @@
       <c r="E343" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F343" s="3">
+      <c r="F343" s="7">
         <v>46059</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A344" s="4" t="s">
+      <c r="A344" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B344" s="4" t="s">
+      <c r="B344" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C344" s="4" t="s">
+      <c r="C344" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D344" s="4" t="s">
+      <c r="D344" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E344" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F344" s="5">
+      <c r="E344" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F344" s="6">
         <v>46059</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C345" s="4" t="s">
+      <c r="C345" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D345" s="4" t="s">
+      <c r="D345" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E345" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F345" s="5">
+      <c r="E345" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F345" s="6">
         <v>46059</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A346" s="4" t="s">
+      <c r="A346" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="B346" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C346" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D346" s="4" t="s">
+      <c r="C346" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D346" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E346" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F346" s="5">
+      <c r="E346" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F346" s="6">
         <v>46059</v>
       </c>
     </row>
@@ -7897,27 +7921,27 @@
       <c r="E347" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F347" s="3">
+      <c r="F347" s="7">
         <v>46069</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A348" s="4" t="s">
+      <c r="A348" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C348" s="4" t="s">
+      <c r="C348" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D348" s="4" t="s">
+      <c r="D348" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E348" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F348" s="5">
+      <c r="E348" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F348" s="6">
         <v>46069</v>
       </c>
     </row>
@@ -7937,27 +7961,27 @@
       <c r="E349" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F349" s="3">
+      <c r="F349" s="7">
         <v>46069</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A350" s="4" t="s">
+      <c r="A350" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C350" s="4" t="s">
+      <c r="C350" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D350" s="4" t="s">
+      <c r="D350" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E350" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F350" s="5">
+      <c r="E350" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F350" s="6">
         <v>46069</v>
       </c>
     </row>
@@ -7977,27 +8001,27 @@
       <c r="E351" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F351" s="3">
+      <c r="F351" s="7">
         <v>46069</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C352" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D352" s="4" t="s">
+      <c r="C352" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D352" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E352" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F352" s="5">
+      <c r="E352" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F352" s="6">
         <v>46069</v>
       </c>
     </row>
@@ -8017,27 +8041,27 @@
       <c r="E353" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F353" s="3">
+      <c r="F353" s="7">
         <v>46069</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" s="4" t="s">
+      <c r="A354" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C354" s="4" t="s">
+      <c r="C354" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D354" s="4" t="s">
+      <c r="D354" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E354" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F354" s="5">
+      <c r="E354" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F354" s="6">
         <v>46069</v>
       </c>
     </row>
@@ -8057,27 +8081,27 @@
       <c r="E355" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F355" s="3">
+      <c r="F355" s="7">
         <v>46070</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" s="4" t="s">
+      <c r="A356" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C356" s="4" t="s">
+      <c r="C356" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D356" s="4" t="s">
+      <c r="D356" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E356" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F356" s="5">
+      <c r="E356" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F356" s="6">
         <v>46070</v>
       </c>
     </row>
@@ -8097,27 +8121,27 @@
       <c r="E357" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F357" s="3">
+      <c r="F357" s="7">
         <v>46070</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" s="4" t="s">
+      <c r="A358" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C358" s="4" t="s">
+      <c r="C358" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D358" s="4" t="s">
+      <c r="D358" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E358" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F358" s="5">
+      <c r="E358" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F358" s="6">
         <v>46070</v>
       </c>
     </row>
@@ -8137,27 +8161,27 @@
       <c r="E359" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F359" s="3">
+      <c r="F359" s="7">
         <v>46081</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A360" s="4" t="s">
+      <c r="A360" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="C360" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D360" s="4" t="s">
+      <c r="D360" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E360" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F360" s="5">
+      <c r="E360" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F360" s="6">
         <v>46081</v>
       </c>
     </row>
@@ -8177,27 +8201,27 @@
       <c r="E361" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F361" s="3">
+      <c r="F361" s="7">
         <v>46081</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A362" s="4" t="s">
+      <c r="A362" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C362" s="4" t="s">
+      <c r="C362" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D362" s="4" t="s">
+      <c r="D362" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E362" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F362" s="5">
+      <c r="E362" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F362" s="6">
         <v>46081</v>
       </c>
     </row>
@@ -8217,7 +8241,7 @@
       <c r="E363" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F363" s="3">
+      <c r="F363" s="7">
         <v>46091</v>
       </c>
     </row>
@@ -8237,47 +8261,47 @@
       <c r="E364" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F364" s="3">
+      <c r="F364" s="7">
         <v>46091</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A365" s="4" t="s">
+      <c r="A365" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C365" s="4" t="s">
+      <c r="C365" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D365" s="4" t="s">
+      <c r="D365" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E365" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F365" s="5">
+      <c r="E365" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F365" s="6">
         <v>46091</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A366" s="4" t="s">
+      <c r="A366" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C366" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D366" s="4" t="s">
+      <c r="C366" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D366" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E366" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F366" s="5">
+      <c r="E366" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F366" s="6">
         <v>46091</v>
       </c>
     </row>
@@ -8297,27 +8321,27 @@
       <c r="E367" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F367" s="3">
+      <c r="F367" s="7">
         <v>46101</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A368" s="4" t="s">
+      <c r="A368" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B368" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C368" s="4" t="s">
+      <c r="C368" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D368" s="4" t="s">
+      <c r="D368" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E368" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F368" s="5">
+      <c r="E368" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F368" s="6">
         <v>46101</v>
       </c>
     </row>
@@ -8337,27 +8361,27 @@
       <c r="E369" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F369" s="3">
+      <c r="F369" s="7">
         <v>46101</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A370" s="4" t="s">
+      <c r="A370" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B370" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C370" s="4" t="s">
+      <c r="C370" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D370" s="4" t="s">
+      <c r="D370" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E370" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F370" s="5">
+      <c r="E370" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F370" s="6">
         <v>46101</v>
       </c>
     </row>
@@ -8377,7 +8401,7 @@
       <c r="E371" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F371" s="3">
+      <c r="F371" s="7">
         <v>46102</v>
       </c>
     </row>
@@ -8397,407 +8421,407 @@
       <c r="E372" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F372" s="3">
+      <c r="F372" s="7">
         <v>46102</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A373" s="4" t="s">
+      <c r="A373" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B373" s="4" t="s">
+      <c r="B373" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C373" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D373" s="4" t="s">
+      <c r="C373" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D373" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E373" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F373" s="5">
+      <c r="E373" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F373" s="6">
         <v>46102</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A374" s="4" t="s">
+      <c r="A374" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="B374" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C374" s="4" t="s">
+      <c r="C374" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D374" s="4" t="s">
+      <c r="D374" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E374" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F374" s="5">
+      <c r="E374" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F374" s="6">
         <v>46102</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" s="8" t="s">
+      <c r="A375" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B375" s="8" t="s">
+      <c r="B375" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C375" s="8" t="s">
+      <c r="C375" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D375" s="8" t="s">
+      <c r="D375" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E375" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F375" s="9">
+      <c r="E375" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F375" s="8">
         <v>46102</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A376" s="6" t="s">
+      <c r="A376" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B376" s="6" t="s">
+      <c r="B376" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C376" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D376" s="6" t="s">
+      <c r="C376" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D376" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E376" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F376" s="7">
+      <c r="E376" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F376" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A377" s="6" t="s">
+      <c r="A377" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B377" s="6" t="s">
+      <c r="B377" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C377" s="6" t="s">
+      <c r="C377" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D377" s="6" t="s">
+      <c r="D377" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E377" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F377" s="7">
+      <c r="E377" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F377" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A378" s="6" t="s">
+      <c r="A378" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B378" s="6" t="s">
+      <c r="B378" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C378" s="6" t="s">
+      <c r="C378" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D378" s="6" t="s">
+      <c r="D378" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E378" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F378" s="7">
+      <c r="E378" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F378" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A379" s="8" t="s">
+      <c r="A379" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B379" s="8" t="s">
+      <c r="B379" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C379" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D379" s="8" t="s">
+      <c r="C379" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D379" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E379" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F379" s="9">
+      <c r="E379" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F379" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A380" s="8" t="s">
+      <c r="A380" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B380" s="8" t="s">
+      <c r="B380" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C380" s="8" t="s">
+      <c r="C380" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D380" s="8" t="s">
+      <c r="D380" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E380" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F380" s="9">
+      <c r="E380" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F380" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A381" s="8" t="s">
+      <c r="A381" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B381" s="8" t="s">
+      <c r="B381" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C381" s="8" t="s">
+      <c r="C381" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D381" s="8" t="s">
+      <c r="D381" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E381" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F381" s="9">
+      <c r="E381" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F381" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A382" s="6" t="s">
+      <c r="A382" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B382" s="6" t="s">
+      <c r="B382" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C382" s="6" t="s">
+      <c r="C382" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D382" s="6" t="s">
+      <c r="D382" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E382" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F382" s="7">
+      <c r="E382" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F382" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A383" s="6" t="s">
+      <c r="A383" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B383" s="6" t="s">
+      <c r="B383" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C383" s="6" t="s">
+      <c r="C383" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D383" s="6" t="s">
+      <c r="D383" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E383" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F383" s="7">
+      <c r="E383" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F383" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A384" s="8" t="s">
+      <c r="A384" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B384" s="8" t="s">
+      <c r="B384" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C384" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D384" s="8" t="s">
+      <c r="C384" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D384" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E384" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F384" s="9">
+      <c r="E384" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F384" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A385" s="8" t="s">
+      <c r="A385" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B385" s="8" t="s">
+      <c r="B385" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C385" s="8" t="s">
+      <c r="C385" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D385" s="8" t="s">
+      <c r="D385" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E385" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F385" s="9">
+      <c r="E385" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F385" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" s="8" t="s">
+      <c r="A386" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B386" s="8" t="s">
+      <c r="B386" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C386" s="8" t="s">
+      <c r="C386" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D386" s="8" t="s">
+      <c r="D386" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E386" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F386" s="9">
+      <c r="E386" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F386" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A387" s="6" t="s">
+      <c r="A387" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B387" s="6" t="s">
+      <c r="B387" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C387" s="6" t="s">
+      <c r="C387" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D387" s="6" t="s">
+      <c r="D387" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E387" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F387" s="7">
+      <c r="E387" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F387" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A388" s="6" t="s">
+      <c r="A388" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B388" s="6" t="s">
+      <c r="B388" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C388" s="6" t="s">
+      <c r="C388" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D388" s="6" t="s">
+      <c r="D388" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E388" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F388" s="7">
+      <c r="E388" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F388" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A389" s="6" t="s">
+      <c r="A389" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B389" s="6" t="s">
+      <c r="B389" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C389" s="6" t="s">
+      <c r="C389" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D389" s="6" t="s">
+      <c r="D389" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E389" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F389" s="7">
+      <c r="E389" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F389" s="9">
         <v>46143</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" s="8" t="s">
+      <c r="A390" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B390" s="8" t="s">
+      <c r="B390" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C390" s="8" t="s">
+      <c r="C390" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D390" s="8" t="s">
+      <c r="D390" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E390" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F390" s="9">
+      <c r="E390" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F390" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A391" s="8" t="s">
+      <c r="A391" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B391" s="8" t="s">
+      <c r="B391" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C391" s="8" t="s">
+      <c r="C391" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D391" s="8" t="s">
+      <c r="D391" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E391" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F391" s="9">
+      <c r="E391" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F391" s="8">
         <v>46143</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A392" s="8" t="s">
+      <c r="A392" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B392" s="8" t="s">
+      <c r="B392" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C392" s="8" t="s">
+      <c r="C392" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D392" s="8" t="s">
+      <c r="D392" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E392" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F392" s="9">
+      <c r="E392" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F392" s="8">
         <v>46143</v>
       </c>
     </row>
@@ -8814,10 +8838,10 @@
       <c r="D393" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E393" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F393" s="3">
+      <c r="E393" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F393" s="7">
         <v>46172</v>
       </c>
     </row>
@@ -8834,10 +8858,10 @@
       <c r="D394" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E394" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F394" s="3">
+      <c r="E394" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F394" s="7">
         <v>46172</v>
       </c>
     </row>
@@ -8854,50 +8878,50 @@
       <c r="D395" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E395" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F395" s="3">
+      <c r="E395" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F395" s="7">
         <v>46172</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A396" s="4" t="s">
+      <c r="A396" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B396" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C396" s="4" t="s">
+      <c r="C396" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D396" s="4" t="s">
+      <c r="D396" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E396" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F396" s="5">
+      <c r="E396" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F396" s="6">
         <v>46172</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A397" s="4" t="s">
+      <c r="A397" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B397" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C397" s="4" t="s">
+      <c r="C397" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D397" s="4" t="s">
+      <c r="D397" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E397" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F397" s="5">
+      <c r="E397" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F397" s="6">
         <v>46172</v>
       </c>
     </row>
@@ -8914,10 +8938,10 @@
       <c r="D398" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E398" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F398" s="3">
+      <c r="E398" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F398" s="7">
         <v>46172</v>
       </c>
     </row>
@@ -8934,12 +8958,496 @@
       <c r="D399" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E399" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F399" s="3">
+      <c r="E399" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F399" s="7">
         <v>46172</v>
       </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A400" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D400" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E400" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F400" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A401" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E401" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F401" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A402" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F402" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A403" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F403" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A404" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E404" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F404" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A405" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D405" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E405" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F405" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A406" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D406" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E406" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F406" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A407" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E407" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F407" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A408" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E408" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F408" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A409" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E409" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F409" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A410" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D410" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E410" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F410" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A411" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E411" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F411" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A412" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D412" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E412" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F412" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A413" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E413" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F413" s="9">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A414" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E414" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F414" s="9">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A415" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E415" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F415" s="9">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A416" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D416" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E416" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F416" s="8">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E417" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F417" s="9">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D418" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E418" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F418" s="8">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E419" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F419" s="9">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D420" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E420" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F420" s="8">
+        <v>46175</v>
+      </c>
+      <c r="G420" s="11"/>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B421" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C421" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D421" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E421" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F421" s="12">
+        <v>46176</v>
+      </c>
+      <c r="G421" s="11"/>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B422" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C422" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D422" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E422" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F422" s="12">
+        <v>46176</v>
+      </c>
+      <c r="G422" s="11"/>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B423" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C423" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D423" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E423" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F423" s="12">
+        <v>46176</v>
+      </c>
+      <c r="G423" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F332E423-91C7-4408-8150-532DBE1DDE01}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="171">
   <si>
     <t>Wizards</t>
   </si>
@@ -537,6 +537,18 @@
   </si>
   <si>
     <t>AMKAL</t>
+  </si>
+  <si>
+    <t>Immortals</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Into The Beach</t>
+  </si>
+  <si>
+    <t>Aether</t>
   </si>
 </sst>
 </file>
@@ -604,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -633,13 +645,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,6 +661,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -974,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:G423"/>
+  <dimension ref="A1:G437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -9318,7 +9328,7 @@
       <c r="D417" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E417" s="10" t="s">
+      <c r="E417" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F417" s="9">
@@ -9358,7 +9368,7 @@
       <c r="D419" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E419" s="10" t="s">
+      <c r="E419" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F419" s="9">
@@ -9384,73 +9394,354 @@
       <c r="F420" s="8">
         <v>46175</v>
       </c>
-      <c r="G420" s="11"/>
+      <c r="G420" s="10"/>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A421" s="10" t="s">
+      <c r="A421" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B421" s="10" t="s">
+      <c r="B421" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C421" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D421" s="10" t="s">
+      <c r="C421" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D421" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E421" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F421" s="12">
+      <c r="E421" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F421" s="9">
         <v>46176</v>
       </c>
-      <c r="G421" s="11"/>
+      <c r="G421" s="10"/>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A422" s="10" t="s">
+      <c r="A422" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B422" s="10" t="s">
+      <c r="B422" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C422" s="10" t="s">
+      <c r="C422" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D422" s="10" t="s">
+      <c r="D422" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E422" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F422" s="12">
+      <c r="E422" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F422" s="9">
         <v>46176</v>
       </c>
-      <c r="G422" s="11"/>
+      <c r="G422" s="10"/>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A423" s="10" t="s">
+      <c r="A423" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B423" s="10" t="s">
+      <c r="B423" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C423" s="10" t="s">
+      <c r="C423" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D423" s="10" t="s">
+      <c r="D423" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E423" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F423" s="12">
+      <c r="E423" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F423" s="9">
         <v>46176</v>
       </c>
-      <c r="G423" s="11"/>
+      <c r="G423" s="10"/>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D424" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E424" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F424" s="6">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F425" s="7">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D426" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E426" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F426" s="6">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F427" s="7">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D428" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E428" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F428" s="6">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E429" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F429" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D430" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E430" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F430" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F431" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D432" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E432" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F432" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A433" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E433" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F433" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A434" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E434" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F434" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A435" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E435" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F435" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A436" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E436" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F436" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A437" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E437" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F437" s="6">
+        <v>46184</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F332E423-91C7-4408-8150-532DBE1DDE01}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8631242F-CAEF-4C98-9C4C-56E62B492753}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="174">
   <si>
     <t>Team 1</t>
   </si>
@@ -549,13 +549,22 @@
   </si>
   <si>
     <t>Aether</t>
+  </si>
+  <si>
+    <t>paiN Academy</t>
+  </si>
+  <si>
+    <t>Sprout</t>
+  </si>
+  <si>
+    <t>Counter Logic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -646,6 +655,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,8 +992,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:G437"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G442"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" style="1" customWidth="1"/>
@@ -991,7 +1003,7 @@
     <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1011,7 +1023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1031,7 +1043,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1051,7 +1063,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1071,7 +1083,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1091,7 +1103,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1111,7 +1123,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1131,7 +1143,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1151,7 +1163,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1171,7 +1183,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -1191,7 +1203,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1211,7 +1223,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1231,7 +1243,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1251,7 +1263,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -1271,7 +1283,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
@@ -1291,7 +1303,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>52</v>
       </c>
@@ -1311,7 +1323,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1331,7 +1343,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>59</v>
       </c>
@@ -1351,7 +1363,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
@@ -1371,7 +1383,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>65</v>
       </c>
@@ -1391,7 +1403,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>67</v>
       </c>
@@ -1411,7 +1423,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -1431,7 +1443,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>71</v>
       </c>
@@ -1451,7 +1463,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>74</v>
       </c>
@@ -1471,7 +1483,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -1491,7 +1503,7 @@
         <v>46025</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -1511,7 +1523,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>81</v>
       </c>
@@ -1531,7 +1543,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>83</v>
       </c>
@@ -1551,7 +1563,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>86</v>
       </c>
@@ -1571,7 +1583,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
@@ -1591,7 +1603,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -1611,7 +1623,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>93</v>
       </c>
@@ -1631,7 +1643,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>95</v>
       </c>
@@ -1651,7 +1663,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>97</v>
       </c>
@@ -1671,7 +1683,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>99</v>
       </c>
@@ -1691,7 +1703,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>102</v>
       </c>
@@ -1711,7 +1723,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>104</v>
       </c>
@@ -1731,7 +1743,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>107</v>
       </c>
@@ -1751,7 +1763,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
@@ -1771,7 +1783,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
@@ -1791,7 +1803,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
@@ -1811,7 +1823,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>115</v>
       </c>
@@ -1831,7 +1843,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
@@ -1851,7 +1863,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>119</v>
       </c>
@@ -1871,7 +1883,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
@@ -1891,7 +1903,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>124</v>
       </c>
@@ -1911,7 +1923,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>126</v>
       </c>
@@ -1931,7 +1943,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>128</v>
       </c>
@@ -1951,7 +1963,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>130</v>
       </c>
@@ -1971,7 +1983,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>132</v>
       </c>
@@ -1991,7 +2003,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>135</v>
       </c>
@@ -2011,7 +2023,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>137</v>
       </c>
@@ -2031,7 +2043,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>139</v>
       </c>
@@ -2051,7 +2063,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>141</v>
       </c>
@@ -2071,7 +2083,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>143</v>
       </c>
@@ -2091,7 +2103,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>145</v>
       </c>
@@ -2111,7 +2123,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>147</v>
       </c>
@@ -2131,7 +2143,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -2151,7 +2163,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -2171,7 +2183,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -2191,7 +2203,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -2211,7 +2223,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>36</v>
       </c>
@@ -2231,7 +2243,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>6</v>
       </c>
@@ -2251,7 +2263,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>6</v>
       </c>
@@ -2271,7 +2283,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>25</v>
       </c>
@@ -2291,7 +2303,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>25</v>
       </c>
@@ -2311,7 +2323,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>25</v>
       </c>
@@ -2331,7 +2343,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>14</v>
       </c>
@@ -2351,7 +2363,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +2383,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>14</v>
       </c>
@@ -2391,7 +2403,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -2411,7 +2423,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -2431,7 +2443,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -2451,7 +2463,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>46</v>
       </c>
@@ -2471,7 +2483,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>46</v>
       </c>
@@ -2491,7 +2503,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>53</v>
       </c>
@@ -2511,7 +2523,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>53</v>
       </c>
@@ -2531,7 +2543,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -2551,7 +2563,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>6</v>
       </c>
@@ -2571,7 +2583,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2591,7 +2603,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>14</v>
       </c>
@@ -2611,7 +2623,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>36</v>
       </c>
@@ -2631,7 +2643,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>36</v>
       </c>
@@ -2651,7 +2663,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>53</v>
       </c>
@@ -2671,7 +2683,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>53</v>
       </c>
@@ -2691,7 +2703,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>20</v>
       </c>
@@ -2711,7 +2723,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>20</v>
       </c>
@@ -2731,7 +2743,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>20</v>
       </c>
@@ -2751,7 +2763,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>34</v>
       </c>
@@ -2771,7 +2783,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>34</v>
       </c>
@@ -2791,7 +2803,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>34</v>
       </c>
@@ -2811,7 +2823,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>40</v>
       </c>
@@ -2831,7 +2843,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>40</v>
       </c>
@@ -2851,7 +2863,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>42</v>
       </c>
@@ -2871,7 +2883,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>42</v>
       </c>
@@ -2891,7 +2903,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>42</v>
       </c>
@@ -2911,7 +2923,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>20</v>
       </c>
@@ -2931,7 +2943,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>20</v>
       </c>
@@ -2951,7 +2963,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>20</v>
       </c>
@@ -2971,7 +2983,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>31</v>
       </c>
@@ -2991,7 +3003,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>31</v>
       </c>
@@ -3011,7 +3023,7 @@
         <v>46033</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>57</v>
       </c>
@@ -3031,7 +3043,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>57</v>
       </c>
@@ -3051,7 +3063,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>40</v>
       </c>
@@ -3071,7 +3083,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>40</v>
       </c>
@@ -3091,7 +3103,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>40</v>
       </c>
@@ -3111,7 +3123,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>42</v>
       </c>
@@ -3131,7 +3143,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>42</v>
       </c>
@@ -3151,7 +3163,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,7 +3183,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>20</v>
       </c>
@@ -3191,7 +3203,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>20</v>
       </c>
@@ -3211,7 +3223,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>34</v>
       </c>
@@ -3231,7 +3243,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>34</v>
       </c>
@@ -3251,7 +3263,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>27</v>
       </c>
@@ -3271,7 +3283,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>27</v>
       </c>
@@ -3291,7 +3303,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>71</v>
       </c>
@@ -3311,7 +3323,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>71</v>
       </c>
@@ -3331,7 +3343,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>71</v>
       </c>
@@ -3351,7 +3363,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>59</v>
       </c>
@@ -3371,7 +3383,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>59</v>
       </c>
@@ -3391,7 +3403,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>74</v>
       </c>
@@ -3411,7 +3423,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>74</v>
       </c>
@@ -3431,7 +3443,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>89</v>
       </c>
@@ -3451,7 +3463,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>89</v>
       </c>
@@ -3471,7 +3483,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>63</v>
       </c>
@@ -3491,7 +3503,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>63</v>
       </c>
@@ -3511,7 +3523,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>93</v>
       </c>
@@ -3531,7 +3543,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>93</v>
       </c>
@@ -3551,7 +3563,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>93</v>
       </c>
@@ -3571,7 +3583,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>69</v>
       </c>
@@ -3591,7 +3603,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>69</v>
       </c>
@@ -3611,7 +3623,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>71</v>
       </c>
@@ -3631,7 +3643,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>71</v>
       </c>
@@ -3651,7 +3663,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>89</v>
       </c>
@@ -3671,7 +3683,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>89</v>
       </c>
@@ -3691,7 +3703,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>89</v>
       </c>
@@ -3711,7 +3723,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>89</v>
       </c>
@@ -3731,7 +3743,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>80</v>
       </c>
@@ -3751,7 +3763,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,7 +3783,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>69</v>
       </c>
@@ -3791,7 +3803,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>69</v>
       </c>
@@ -3811,7 +3823,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>80</v>
       </c>
@@ -3831,7 +3843,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>80</v>
       </c>
@@ -3851,7 +3863,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>96</v>
       </c>
@@ -3871,7 +3883,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>96</v>
       </c>
@@ -3891,7 +3903,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>96</v>
       </c>
@@ -3911,7 +3923,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>91</v>
       </c>
@@ -3931,7 +3943,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>91</v>
       </c>
@@ -3951,7 +3963,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>65</v>
       </c>
@@ -3971,7 +3983,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>65</v>
       </c>
@@ -3991,7 +4003,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>65</v>
       </c>
@@ -4011,7 +4023,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>78</v>
       </c>
@@ -4031,7 +4043,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>78</v>
       </c>
@@ -4051,7 +4063,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>78</v>
       </c>
@@ -4071,7 +4083,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>91</v>
       </c>
@@ -4091,7 +4103,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>91</v>
       </c>
@@ -4111,7 +4123,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>86</v>
       </c>
@@ -4131,7 +4143,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>86</v>
       </c>
@@ -4151,7 +4163,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>86</v>
       </c>
@@ -4171,7 +4183,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>84</v>
       </c>
@@ -4191,7 +4203,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>84</v>
       </c>
@@ -4211,7 +4223,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>96</v>
       </c>
@@ -4231,7 +4243,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>96</v>
       </c>
@@ -4251,7 +4263,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>96</v>
       </c>
@@ -4271,7 +4283,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>65</v>
       </c>
@@ -4291,7 +4303,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>65</v>
       </c>
@@ -4311,7 +4323,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>78</v>
       </c>
@@ -4331,7 +4343,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>78</v>
       </c>
@@ -4351,7 +4363,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>96</v>
       </c>
@@ -4371,7 +4383,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>96</v>
       </c>
@@ -4391,7 +4403,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>96</v>
       </c>
@@ -4411,7 +4423,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>103</v>
       </c>
@@ -4431,7 +4443,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>103</v>
       </c>
@@ -4451,7 +4463,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>103</v>
       </c>
@@ -4471,7 +4483,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>147</v>
       </c>
@@ -4491,7 +4503,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>147</v>
       </c>
@@ -4511,7 +4523,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>133</v>
       </c>
@@ -4531,7 +4543,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>133</v>
       </c>
@@ -4551,7 +4563,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>133</v>
       </c>
@@ -4571,7 +4583,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>127</v>
       </c>
@@ -4591,7 +4603,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>127</v>
       </c>
@@ -4611,7 +4623,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>147</v>
       </c>
@@ -4631,7 +4643,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>147</v>
       </c>
@@ -4651,7 +4663,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>147</v>
       </c>
@@ -4671,7 +4683,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>133</v>
       </c>
@@ -4691,7 +4703,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>133</v>
       </c>
@@ -4711,7 +4723,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>103</v>
       </c>
@@ -4731,7 +4743,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>103</v>
       </c>
@@ -4751,7 +4763,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>103</v>
       </c>
@@ -4771,7 +4783,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>136</v>
       </c>
@@ -4791,7 +4803,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>136</v>
       </c>
@@ -4811,7 +4823,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>103</v>
       </c>
@@ -4831,7 +4843,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>103</v>
       </c>
@@ -4851,7 +4863,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>147</v>
       </c>
@@ -4871,7 +4883,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>147</v>
       </c>
@@ -4891,7 +4903,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>147</v>
       </c>
@@ -4911,7 +4923,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>129</v>
       </c>
@@ -4931,7 +4943,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>129</v>
       </c>
@@ -4951,7 +4963,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>129</v>
       </c>
@@ -4971,7 +4983,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>103</v>
       </c>
@@ -4991,7 +5003,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>103</v>
       </c>
@@ -5011,7 +5023,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>103</v>
       </c>
@@ -5031,7 +5043,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>112</v>
       </c>
@@ -5051,7 +5063,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>112</v>
       </c>
@@ -5071,7 +5083,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>112</v>
       </c>
@@ -5091,7 +5103,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>105</v>
       </c>
@@ -5111,7 +5123,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>105</v>
       </c>
@@ -5131,7 +5143,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>97</v>
       </c>
@@ -5151,7 +5163,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>97</v>
       </c>
@@ -5171,7 +5183,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>97</v>
       </c>
@@ -5191,7 +5203,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>143</v>
       </c>
@@ -5211,7 +5223,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>143</v>
       </c>
@@ -5231,7 +5243,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>100</v>
       </c>
@@ -5251,7 +5263,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>100</v>
       </c>
@@ -5271,7 +5283,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>141</v>
       </c>
@@ -5291,7 +5303,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>141</v>
       </c>
@@ -5311,7 +5323,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>112</v>
       </c>
@@ -5331,7 +5343,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>112</v>
       </c>
@@ -5351,7 +5363,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>112</v>
       </c>
@@ -5371,7 +5383,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>97</v>
       </c>
@@ -5391,7 +5403,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>97</v>
       </c>
@@ -5411,7 +5423,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>97</v>
       </c>
@@ -5431,7 +5443,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>97</v>
       </c>
@@ -5451,7 +5463,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>97</v>
       </c>
@@ -5471,7 +5483,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>112</v>
       </c>
@@ -5491,7 +5503,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>112</v>
       </c>
@@ -5511,7 +5523,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>105</v>
       </c>
@@ -5531,7 +5543,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>105</v>
       </c>
@@ -5551,7 +5563,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>100</v>
       </c>
@@ -5571,7 +5583,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>100</v>
       </c>
@@ -5591,7 +5603,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>139</v>
       </c>
@@ -5611,7 +5623,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>139</v>
       </c>
@@ -5631,7 +5643,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>124</v>
       </c>
@@ -5651,7 +5663,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>124</v>
       </c>
@@ -5671,7 +5683,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>124</v>
       </c>
@@ -5691,7 +5703,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>138</v>
       </c>
@@ -5711,7 +5723,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>138</v>
       </c>
@@ -5731,7 +5743,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>119</v>
       </c>
@@ -5751,7 +5763,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>119</v>
       </c>
@@ -5771,7 +5783,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>119</v>
       </c>
@@ -5791,7 +5803,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>139</v>
       </c>
@@ -5811,7 +5823,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>139</v>
       </c>
@@ -5831,7 +5843,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>108</v>
       </c>
@@ -5851,7 +5863,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>108</v>
       </c>
@@ -5871,7 +5883,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>108</v>
       </c>
@@ -5891,7 +5903,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>118</v>
       </c>
@@ -5911,7 +5923,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>118</v>
       </c>
@@ -5931,7 +5943,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>118</v>
       </c>
@@ -5951,7 +5963,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>138</v>
       </c>
@@ -5971,7 +5983,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>138</v>
       </c>
@@ -5991,7 +6003,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>138</v>
       </c>
@@ -6011,7 +6023,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>139</v>
       </c>
@@ -6031,7 +6043,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>139</v>
       </c>
@@ -6051,7 +6063,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>139</v>
       </c>
@@ -6071,7 +6083,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>109</v>
       </c>
@@ -6091,7 +6103,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>109</v>
       </c>
@@ -6111,7 +6123,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>109</v>
       </c>
@@ -6131,7 +6143,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>118</v>
       </c>
@@ -6151,7 +6163,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>118</v>
       </c>
@@ -6171,7 +6183,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>138</v>
       </c>
@@ -6191,7 +6203,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>138</v>
       </c>
@@ -6211,7 +6223,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>145</v>
       </c>
@@ -6231,7 +6243,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>145</v>
       </c>
@@ -6251,7 +6263,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>83</v>
       </c>
@@ -6271,7 +6283,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>83</v>
       </c>
@@ -6291,7 +6303,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>92</v>
       </c>
@@ -6311,7 +6323,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>92</v>
       </c>
@@ -6331,7 +6343,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>92</v>
       </c>
@@ -6351,7 +6363,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>66</v>
       </c>
@@ -6371,7 +6383,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>66</v>
       </c>
@@ -6391,7 +6403,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>94</v>
       </c>
@@ -6411,7 +6423,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>94</v>
       </c>
@@ -6431,7 +6443,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>94</v>
       </c>
@@ -6451,7 +6463,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>92</v>
       </c>
@@ -6471,7 +6483,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>92</v>
       </c>
@@ -6491,7 +6503,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>92</v>
       </c>
@@ -6511,7 +6523,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>94</v>
       </c>
@@ -6531,7 +6543,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>94</v>
       </c>
@@ -6551,7 +6563,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>65</v>
       </c>
@@ -6571,7 +6583,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>65</v>
       </c>
@@ -6591,7 +6603,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>59</v>
       </c>
@@ -6611,7 +6623,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,7 +6643,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>103</v>
       </c>
@@ -6651,7 +6663,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>103</v>
       </c>
@@ -6671,7 +6683,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>103</v>
       </c>
@@ -6691,7 +6703,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>138</v>
       </c>
@@ -6711,7 +6723,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>138</v>
       </c>
@@ -6731,7 +6743,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>138</v>
       </c>
@@ -6751,7 +6763,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>65</v>
       </c>
@@ -6771,7 +6783,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>65</v>
       </c>
@@ -6791,7 +6803,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>103</v>
       </c>
@@ -6811,7 +6823,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>103</v>
       </c>
@@ -6831,7 +6843,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>103</v>
       </c>
@@ -6851,7 +6863,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>31</v>
       </c>
@@ -6871,7 +6883,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>96</v>
       </c>
@@ -6891,7 +6903,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>100</v>
       </c>
@@ -6911,7 +6923,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>20</v>
       </c>
@@ -6931,7 +6943,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>109</v>
       </c>
@@ -6951,7 +6963,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>129</v>
       </c>
@@ -6971,7 +6983,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>93</v>
       </c>
@@ -6991,7 +7003,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>14</v>
       </c>
@@ -7011,7 +7023,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>147</v>
       </c>
@@ -7031,7 +7043,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>96</v>
       </c>
@@ -7051,7 +7063,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>20</v>
       </c>
@@ -7071,7 +7083,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>31</v>
       </c>
@@ -7091,7 +7103,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>78</v>
       </c>
@@ -7111,7 +7123,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>14</v>
       </c>
@@ -7131,7 +7143,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>36</v>
       </c>
@@ -7151,7 +7163,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>109</v>
       </c>
@@ -7171,7 +7183,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>20</v>
       </c>
@@ -7191,7 +7203,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>20</v>
       </c>
@@ -7211,7 +7223,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>100</v>
       </c>
@@ -7231,7 +7243,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>100</v>
       </c>
@@ -7251,7 +7263,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>100</v>
       </c>
@@ -7271,7 +7283,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>93</v>
       </c>
@@ -7291,7 +7303,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>78</v>
       </c>
@@ -7311,7 +7323,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>147</v>
       </c>
@@ -7331,7 +7343,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>96</v>
       </c>
@@ -7351,7 +7363,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>103</v>
       </c>
@@ -7371,7 +7383,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>103</v>
       </c>
@@ -7391,7 +7403,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>80</v>
       </c>
@@ -7411,7 +7423,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>80</v>
       </c>
@@ -7431,7 +7443,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>80</v>
       </c>
@@ -7451,7 +7463,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>147</v>
       </c>
@@ -7471,7 +7483,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>147</v>
       </c>
@@ -7491,7 +7503,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>147</v>
       </c>
@@ -7511,7 +7523,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>31</v>
       </c>
@@ -7531,7 +7543,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>31</v>
       </c>
@@ -7551,7 +7563,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>36</v>
       </c>
@@ -7571,7 +7583,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>36</v>
       </c>
@@ -7591,7 +7603,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>93</v>
       </c>
@@ -7611,7 +7623,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>93</v>
       </c>
@@ -7631,7 +7643,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>93</v>
       </c>
@@ -7651,7 +7663,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>121</v>
       </c>
@@ -7671,7 +7683,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>121</v>
       </c>
@@ -7691,7 +7703,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>129</v>
       </c>
@@ -7711,7 +7723,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>129</v>
       </c>
@@ -7731,7 +7743,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>129</v>
       </c>
@@ -7751,7 +7763,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>31</v>
       </c>
@@ -7771,7 +7783,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>31</v>
       </c>
@@ -7791,7 +7803,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>31</v>
       </c>
@@ -7811,7 +7823,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>78</v>
       </c>
@@ -7831,7 +7843,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>78</v>
       </c>
@@ -7851,7 +7863,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>36</v>
       </c>
@@ -7871,7 +7883,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>36</v>
       </c>
@@ -7891,7 +7903,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>36</v>
       </c>
@@ -7911,7 +7923,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>34</v>
       </c>
@@ -7931,7 +7943,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>105</v>
       </c>
@@ -7951,7 +7963,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>67</v>
       </c>
@@ -7971,7 +7983,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>118</v>
       </c>
@@ -7991,7 +8003,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>69</v>
       </c>
@@ -8011,7 +8023,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>130</v>
       </c>
@@ -8031,7 +8043,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>94</v>
       </c>
@@ -8051,7 +8063,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>25</v>
       </c>
@@ -8071,7 +8083,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>34</v>
       </c>
@@ -8091,7 +8103,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>69</v>
       </c>
@@ -8111,7 +8123,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>105</v>
       </c>
@@ -8131,7 +8143,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>25</v>
       </c>
@@ -8151,7 +8163,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>100</v>
       </c>
@@ -8171,7 +8183,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>65</v>
       </c>
@@ -8191,7 +8203,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>118</v>
       </c>
@@ -8211,7 +8223,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>129</v>
       </c>
@@ -8231,7 +8243,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>147</v>
       </c>
@@ -8251,7 +8263,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>147</v>
       </c>
@@ -8271,7 +8283,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>25</v>
       </c>
@@ -8291,7 +8303,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>25</v>
       </c>
@@ -8311,7 +8323,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>67</v>
       </c>
@@ -8331,7 +8343,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>130</v>
       </c>
@@ -8351,7 +8363,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>94</v>
       </c>
@@ -8371,7 +8383,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>20</v>
       </c>
@@ -8391,7 +8403,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>118</v>
       </c>
@@ -8411,7 +8423,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>118</v>
       </c>
@@ -8431,7 +8443,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>129</v>
       </c>
@@ -8451,7 +8463,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>129</v>
       </c>
@@ -8471,7 +8483,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>129</v>
       </c>
@@ -8491,7 +8503,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>20</v>
       </c>
@@ -8511,7 +8523,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>20</v>
       </c>
@@ -8531,7 +8543,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>20</v>
       </c>
@@ -8551,7 +8563,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="379" spans="1:6">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
         <v>34</v>
       </c>
@@ -8571,7 +8583,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
         <v>34</v>
       </c>
@@ -8591,7 +8603,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
         <v>34</v>
       </c>
@@ -8611,7 +8623,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>69</v>
       </c>
@@ -8631,7 +8643,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
         <v>69</v>
       </c>
@@ -8651,7 +8663,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
         <v>78</v>
       </c>
@@ -8671,7 +8683,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
         <v>78</v>
       </c>
@@ -8691,7 +8703,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
         <v>78</v>
       </c>
@@ -8711,7 +8723,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
         <v>105</v>
       </c>
@@ -8731,7 +8743,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>105</v>
       </c>
@@ -8751,7 +8763,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
         <v>105</v>
       </c>
@@ -8771,7 +8783,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
         <v>130</v>
       </c>
@@ -8791,7 +8803,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>130</v>
       </c>
@@ -8811,7 +8823,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
         <v>130</v>
       </c>
@@ -8831,7 +8843,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>36</v>
       </c>
@@ -8851,7 +8863,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>36</v>
       </c>
@@ -8871,7 +8883,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>36</v>
       </c>
@@ -8891,7 +8903,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>96</v>
       </c>
@@ -8911,7 +8923,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>96</v>
       </c>
@@ -8931,7 +8943,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>20</v>
       </c>
@@ -8951,7 +8963,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>20</v>
       </c>
@@ -8971,7 +8983,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
         <v>147</v>
       </c>
@@ -8991,7 +9003,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
         <v>147</v>
       </c>
@@ -9011,7 +9023,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>65</v>
       </c>
@@ -9031,7 +9043,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
         <v>65</v>
       </c>
@@ -9051,7 +9063,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>65</v>
       </c>
@@ -9071,7 +9083,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
         <v>130</v>
       </c>
@@ -9091,7 +9103,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
         <v>130</v>
       </c>
@@ -9111,7 +9123,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
         <v>100</v>
       </c>
@@ -9131,7 +9143,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="408" spans="1:6">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>100</v>
       </c>
@@ -9151,7 +9163,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="409" spans="1:6">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>100</v>
       </c>
@@ -9171,7 +9183,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="410" spans="1:6">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
         <v>94</v>
       </c>
@@ -9191,7 +9203,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="411" spans="1:6">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>94</v>
       </c>
@@ -9211,7 +9223,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="412" spans="1:6">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
         <v>94</v>
       </c>
@@ -9231,7 +9243,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="413" spans="1:6">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
         <v>25</v>
       </c>
@@ -9251,7 +9263,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="414" spans="1:6">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>25</v>
       </c>
@@ -9271,7 +9283,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="415" spans="1:6">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
         <v>25</v>
       </c>
@@ -9291,7 +9303,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="416" spans="1:6">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
         <v>28</v>
       </c>
@@ -9311,7 +9323,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>165</v>
       </c>
@@ -9331,7 +9343,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>163</v>
       </c>
@@ -9351,7 +9363,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
         <v>28</v>
       </c>
@@ -9371,7 +9383,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
         <v>28</v>
       </c>
@@ -9392,7 +9404,7 @@
       </c>
       <c r="G420" s="10"/>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>94</v>
       </c>
@@ -9413,7 +9425,7 @@
       </c>
       <c r="G421" s="10"/>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>94</v>
       </c>
@@ -9434,7 +9446,7 @@
       </c>
       <c r="G422" s="10"/>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
         <v>94</v>
       </c>
@@ -9455,7 +9467,7 @@
       </c>
       <c r="G423" s="10"/>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
         <v>33</v>
       </c>
@@ -9475,7 +9487,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>116</v>
       </c>
@@ -9495,7 +9507,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
         <v>168</v>
       </c>
@@ -9515,7 +9527,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
         <v>33</v>
       </c>
@@ -9535,7 +9547,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
         <v>168</v>
       </c>
@@ -9555,7 +9567,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
         <v>19</v>
       </c>
@@ -9575,7 +9587,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
         <v>11</v>
       </c>
@@ -9595,7 +9607,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
         <v>19</v>
       </c>
@@ -9615,7 +9627,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
         <v>11</v>
       </c>
@@ -9635,7 +9647,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>19</v>
       </c>
@@ -9655,7 +9667,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="434" spans="1:6">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>69</v>
       </c>
@@ -9675,7 +9687,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="435" spans="1:6">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>69</v>
       </c>
@@ -9695,7 +9707,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="436" spans="1:6">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>69</v>
       </c>
@@ -9715,7 +9727,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="437" spans="1:6">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>69</v>
       </c>
@@ -9733,6 +9745,106 @@
       </c>
       <c r="F437" s="6">
         <v>46184</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E438" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F438" s="7">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A439" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D439" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E439" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F439" s="7">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E440" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F440" s="7">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A441" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F441" s="7">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E442" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F442" s="7">
+        <v>46214</v>
       </c>
     </row>
   </sheetData>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Braga\OneDrive\Documentos\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{61EBEDED-D714-4DCB-AEF2-54558292FAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8631242F-CAEF-4C98-9C4C-56E62B492753}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="174">
   <si>
     <t>Team 1</t>
   </si>
@@ -564,7 +564,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,6 +588,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -625,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -655,9 +662,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -992,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:G442"/>
+  <dimension ref="A1:G463"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -9760,7 +9771,7 @@
       <c r="D438" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E438" s="11" t="s">
+      <c r="E438" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F438" s="7">
@@ -9783,7 +9794,7 @@
       <c r="E439" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F439" s="7">
+      <c r="F439" s="6">
         <v>46214</v>
       </c>
     </row>
@@ -9800,7 +9811,7 @@
       <c r="D440" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E440" s="11" t="s">
+      <c r="E440" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F440" s="7">
@@ -9823,7 +9834,7 @@
       <c r="E441" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F441" s="7">
+      <c r="F441" s="6">
         <v>46214</v>
       </c>
     </row>
@@ -9840,12 +9851,422 @@
       <c r="D442" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E442" s="11" t="s">
+      <c r="E442" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F442" s="7">
         <v>46214</v>
       </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A443" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D443" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E443" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F443" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A444" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D444" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E444" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F444" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A445" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E445" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F445" s="9">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A446" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E446" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F446" s="9">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A447" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D447" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E447" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F447" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A448" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D448" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E448" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F448" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D449" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E449" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F449" s="8">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E450" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F450" s="9">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E451" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F451" s="9">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E452" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F452" s="9">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D453" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E453" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F453" s="8">
+        <v>46216</v>
+      </c>
+      <c r="G453" s="10"/>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D454" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E454" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F454" s="8">
+        <v>46216</v>
+      </c>
+      <c r="G454" s="10"/>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C455" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E455" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F455" s="9">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E456" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F456" s="9">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D457" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E457" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F457" s="8">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D458" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E458" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F458" s="8">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D459" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E459" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F459" s="8">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E460" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F460" s="9">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C461" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D461" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E461" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F461" s="9">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E462" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F462" s="9">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463" s="11"/>
+      <c r="B463" s="11"/>
+      <c r="C463" s="11"/>
+      <c r="D463" s="11"/>
+      <c r="E463" s="13"/>
+      <c r="F463" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Braga\OneDrive\Documentos\GitHub\ck-tools\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAE06C51-1287-4C3D-8F99-72B017C589A6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="209">
   <si>
     <t>Team 1</t>
   </si>
@@ -558,6 +558,111 @@
   </si>
   <si>
     <t>Counter Logic</t>
+  </si>
+  <si>
+    <t>MAD Lions</t>
+  </si>
+  <si>
+    <t>Heroic Academy</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2026</t>
+  </si>
+  <si>
+    <t>Fnatic</t>
+  </si>
+  <si>
+    <t>NIP Impact</t>
+  </si>
+  <si>
+    <t>ENCE Academy</t>
+  </si>
+  <si>
+    <t>100 Thieves</t>
+  </si>
+  <si>
+    <t>SKYFURY</t>
+  </si>
+  <si>
+    <t>FlyQuest RED</t>
+  </si>
+  <si>
+    <t>BIG Academy</t>
+  </si>
+  <si>
+    <t>MOUZ NXT</t>
+  </si>
+  <si>
+    <t>QMISTRY</t>
+  </si>
+  <si>
+    <t>mousesports</t>
+  </si>
+  <si>
+    <t>NOVAQ</t>
+  </si>
+  <si>
+    <t>Gambit</t>
+  </si>
+  <si>
+    <t>Wildcard Academy</t>
+  </si>
+  <si>
+    <t>Nordix</t>
+  </si>
+  <si>
+    <t>VeryGames</t>
+  </si>
+  <si>
+    <t>Astralis Talent</t>
+  </si>
+  <si>
+    <t>Astana Dragons</t>
+  </si>
+  <si>
+    <t>Quantum Bellator Fire</t>
+  </si>
+  <si>
+    <t>Copenhagen Wolves</t>
+  </si>
+  <si>
+    <t>00 Nation</t>
+  </si>
+  <si>
+    <t>Misfits</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>Kinguin</t>
+  </si>
+  <si>
+    <t>Vertigo</t>
+  </si>
+  <si>
+    <t>0x13</t>
+  </si>
+  <si>
+    <t>Space Soldiers</t>
+  </si>
+  <si>
+    <t>Fluffy Gangsters</t>
+  </si>
+  <si>
+    <t>HAVU</t>
+  </si>
+  <si>
+    <t>Movistar KOI</t>
+  </si>
+  <si>
+    <t>GhoulsW</t>
+  </si>
+  <si>
+    <t>Vox Eminor</t>
   </si>
 </sst>
 </file>
@@ -665,10 +770,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,7 +792,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1003,14 +1108,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:G463"/>
+  <dimension ref="A1:H519"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9911,7 +10016,7 @@
       <c r="D445" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E445" s="12" t="s">
+      <c r="E445" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F445" s="9">
@@ -9978,7 +10083,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
         <v>146</v>
       </c>
@@ -9998,7 +10103,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>28</v>
       </c>
@@ -10018,7 +10123,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
         <v>28</v>
       </c>
@@ -10031,14 +10136,14 @@
       <c r="D451" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E451" s="12" t="s">
+      <c r="E451" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F451" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>28</v>
       </c>
@@ -10051,14 +10156,14 @@
       <c r="D452" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E452" s="12" t="s">
+      <c r="E452" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F452" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
         <v>116</v>
       </c>
@@ -10079,7 +10184,7 @@
       </c>
       <c r="G453" s="10"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
         <v>116</v>
       </c>
@@ -10100,7 +10205,7 @@
       </c>
       <c r="G454" s="10"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
         <v>146</v>
       </c>
@@ -10113,14 +10218,14 @@
       <c r="D455" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E455" s="12" t="s">
+      <c r="E455" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F455" s="9">
         <v>46216</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>146</v>
       </c>
@@ -10133,14 +10238,14 @@
       <c r="D456" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E456" s="12" t="s">
+      <c r="E456" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F456" s="9">
         <v>46216</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
         <v>116</v>
       </c>
@@ -10160,7 +10265,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>116</v>
       </c>
@@ -10180,7 +10285,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
         <v>116</v>
       </c>
@@ -10200,7 +10305,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>166</v>
       </c>
@@ -10213,14 +10318,14 @@
       <c r="D460" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E460" s="12" t="s">
+      <c r="E460" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F460" s="9">
         <v>46218</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>166</v>
       </c>
@@ -10233,14 +10338,14 @@
       <c r="D461" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E461" s="12" t="s">
+      <c r="E461" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F461" s="9">
         <v>46218</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>166</v>
       </c>
@@ -10253,20 +10358,854 @@
       <c r="D462" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E462" s="12" t="s">
+      <c r="E462" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F462" s="9">
         <v>46218</v>
       </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A463" s="11"/>
-      <c r="B463" s="11"/>
-      <c r="C463" s="11"/>
-      <c r="D463" s="11"/>
-      <c r="E463" s="13"/>
-      <c r="F463" s="11"/>
+      <c r="G462" s="10"/>
+      <c r="H462" s="10"/>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A463" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B463" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C463" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D463" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E463" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F463" s="13">
+        <v>46219</v>
+      </c>
+      <c r="G463" s="10"/>
+      <c r="H463" s="10"/>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A464" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B464" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C464" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D464" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E464" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F464" s="13">
+        <v>46219</v>
+      </c>
+      <c r="G464" s="10"/>
+      <c r="H464" s="10"/>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A465" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B465" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C465" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D465" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E465" s="11"/>
+      <c r="F465" s="11"/>
+      <c r="G465" s="10"/>
+      <c r="H465" s="10"/>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A466" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B466" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C466" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D466" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E466" s="11"/>
+      <c r="F466" s="11"/>
+      <c r="G466" s="10"/>
+      <c r="H466" s="10"/>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A467" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B467" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C467" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D467" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E467" s="11"/>
+      <c r="F467" s="11"/>
+      <c r="G467" s="10"/>
+      <c r="H467" s="10"/>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A468" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B468" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C468" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D468" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E468" s="11"/>
+      <c r="F468" s="11"/>
+      <c r="G468" s="10"/>
+      <c r="H468" s="10"/>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A469" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B469" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C469" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D469" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E469" s="11"/>
+      <c r="F469" s="11"/>
+      <c r="G469" s="10"/>
+      <c r="H469" s="10"/>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A470" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B470" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C470" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D470" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E470" s="11"/>
+      <c r="F470" s="11"/>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A471" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B471" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C471" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D471" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E471" s="11"/>
+      <c r="F471" s="11"/>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A472" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B472" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C472" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D472" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E472" s="11"/>
+      <c r="F472" s="11"/>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A473" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B473" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C473" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D473" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E473" s="11"/>
+      <c r="F473" s="11"/>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A474" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B474" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C474" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D474" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E474" s="11"/>
+      <c r="F474" s="11"/>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A475" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B475" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C475" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D475" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E475" s="11"/>
+      <c r="F475" s="11"/>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A476" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B476" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C476" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D476" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E476" s="11"/>
+      <c r="F476" s="11"/>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A477" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B477" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C477" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D477" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E477" s="11"/>
+      <c r="F477" s="11"/>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A478" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B478" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C478" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D478" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E478" s="11"/>
+      <c r="F478" s="11"/>
+      <c r="G478" s="12"/>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A479" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B479" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C479" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D479" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E479" s="11"/>
+      <c r="F479" s="11"/>
+      <c r="G479" s="12"/>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A480" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B480" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C480" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D480" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E480" s="11"/>
+      <c r="F480" s="11"/>
+      <c r="G480" s="12"/>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A481" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B481" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C481" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D481" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E481" s="11"/>
+      <c r="F481" s="11"/>
+      <c r="G481" s="12"/>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A482" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B482" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C482" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D482" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E482" s="11"/>
+      <c r="F482" s="11"/>
+      <c r="G482" s="12"/>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A483" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B483" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C483" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D483" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E483" s="11"/>
+      <c r="F483" s="11"/>
+      <c r="G483" s="12"/>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A484" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B484" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C484" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D484" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E484" s="11"/>
+      <c r="F484" s="11"/>
+      <c r="G484" s="12"/>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A485" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B485" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C485" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D485" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E485" s="11"/>
+      <c r="F485" s="11"/>
+      <c r="G485" s="12"/>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A486" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B486" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C486" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D486" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E486" s="11"/>
+      <c r="F486" s="11"/>
+      <c r="G486" s="12"/>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A487" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B487" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C487" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D487" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E487" s="11"/>
+      <c r="F487" s="11"/>
+      <c r="G487" s="12"/>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A488" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B488" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C488" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D488" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E488" s="11"/>
+      <c r="F488" s="11"/>
+      <c r="G488" s="12"/>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A489" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B489" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C489" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D489" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E489" s="11"/>
+      <c r="F489" s="11"/>
+      <c r="G489" s="12"/>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A490" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B490" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C490" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D490" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E490" s="11"/>
+      <c r="F490" s="11"/>
+      <c r="G490" s="12"/>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A491" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B491" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C491" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D491" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E491" s="11"/>
+      <c r="F491" s="11"/>
+      <c r="G491" s="12"/>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A492" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B492" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C492" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D492" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E492" s="11"/>
+      <c r="F492" s="11"/>
+      <c r="G492" s="12"/>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A493" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B493" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C493" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D493" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E493" s="11"/>
+      <c r="F493" s="11"/>
+      <c r="G493" s="12"/>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A494" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B494" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C494" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D494" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E494" s="11"/>
+      <c r="F494" s="11"/>
+      <c r="G494" s="12"/>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A495" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B495" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C495" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D495" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E495" s="11"/>
+      <c r="F495" s="11"/>
+      <c r="G495" s="12"/>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A496" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B496" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C496" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D496" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E496" s="11"/>
+      <c r="F496" s="11"/>
+      <c r="G496" s="12"/>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A497" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B497" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C497" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D497" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E497" s="11"/>
+      <c r="F497" s="11"/>
+      <c r="G497" s="12"/>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A498" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B498" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C498" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D498" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E498" s="11"/>
+      <c r="F498" s="11"/>
+      <c r="G498" s="12"/>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A499" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B499" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C499" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D499" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E499" s="11"/>
+      <c r="F499" s="11"/>
+      <c r="G499" s="12"/>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A500" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B500" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C500" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D500" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E500" s="11"/>
+      <c r="F500" s="11"/>
+      <c r="G500" s="12"/>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A501" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B501" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C501" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D501" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E501" s="11"/>
+      <c r="F501" s="11"/>
+      <c r="G501" s="12"/>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A502" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B502" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C502" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D502" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E502" s="11"/>
+      <c r="F502" s="11"/>
+      <c r="G502" s="12"/>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A503" s="11"/>
+      <c r="B503" s="11"/>
+      <c r="C503" s="11"/>
+      <c r="D503" s="11"/>
+      <c r="E503" s="11"/>
+      <c r="F503" s="11"/>
+      <c r="G503" s="12"/>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A504" s="11"/>
+      <c r="B504" s="11"/>
+      <c r="C504" s="11"/>
+      <c r="D504" s="11"/>
+      <c r="E504" s="11"/>
+      <c r="F504" s="11"/>
+      <c r="G504" s="12"/>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A505" s="11"/>
+      <c r="B505" s="11"/>
+      <c r="C505" s="11"/>
+      <c r="D505" s="11"/>
+      <c r="E505" s="11"/>
+      <c r="F505" s="11"/>
+      <c r="G505" s="12"/>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A506" s="11"/>
+      <c r="B506" s="11"/>
+      <c r="C506" s="11"/>
+      <c r="D506" s="11"/>
+      <c r="E506" s="11"/>
+      <c r="F506" s="11"/>
+      <c r="G506" s="12"/>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A507" s="11"/>
+      <c r="B507" s="11"/>
+      <c r="C507" s="11"/>
+      <c r="D507" s="11"/>
+      <c r="E507" s="11"/>
+      <c r="F507" s="11"/>
+      <c r="G507" s="12"/>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A508" s="11"/>
+      <c r="B508" s="11"/>
+      <c r="C508" s="11"/>
+      <c r="D508" s="11"/>
+      <c r="E508" s="11"/>
+      <c r="F508" s="11"/>
+      <c r="G508" s="12"/>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A509" s="11"/>
+      <c r="B509" s="11"/>
+      <c r="C509" s="11"/>
+      <c r="D509" s="11"/>
+      <c r="E509" s="11"/>
+      <c r="F509" s="11"/>
+      <c r="G509" s="12"/>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510" s="11"/>
+      <c r="B510" s="11"/>
+      <c r="C510" s="11"/>
+      <c r="D510" s="11"/>
+      <c r="E510" s="11"/>
+      <c r="F510" s="11"/>
+      <c r="G510" s="12"/>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A511" s="11"/>
+      <c r="B511" s="11"/>
+      <c r="C511" s="11"/>
+      <c r="D511" s="11"/>
+      <c r="E511" s="11"/>
+      <c r="F511" s="11"/>
+      <c r="G511" s="12"/>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A512" s="11"/>
+      <c r="B512" s="11"/>
+      <c r="C512" s="11"/>
+      <c r="D512" s="11"/>
+      <c r="E512" s="11"/>
+      <c r="F512" s="11"/>
+      <c r="G512" s="12"/>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A513" s="11"/>
+      <c r="B513" s="11"/>
+      <c r="C513" s="11"/>
+      <c r="D513" s="11"/>
+      <c r="E513" s="11"/>
+      <c r="F513" s="11"/>
+      <c r="G513" s="12"/>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A514" s="11"/>
+      <c r="B514" s="11"/>
+      <c r="C514" s="11"/>
+      <c r="D514" s="11"/>
+      <c r="E514" s="11"/>
+      <c r="F514" s="11"/>
+      <c r="G514" s="12"/>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A515" s="11"/>
+      <c r="B515" s="11"/>
+      <c r="C515" s="11"/>
+      <c r="D515" s="11"/>
+      <c r="E515" s="11"/>
+      <c r="F515" s="11"/>
+      <c r="G515" s="12"/>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A516" s="11"/>
+      <c r="B516" s="11"/>
+      <c r="C516" s="11"/>
+      <c r="D516" s="11"/>
+      <c r="E516" s="11"/>
+      <c r="F516" s="11"/>
+      <c r="G516" s="12"/>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A517" s="11"/>
+      <c r="B517" s="11"/>
+      <c r="C517" s="11"/>
+      <c r="D517" s="11"/>
+      <c r="E517" s="11"/>
+      <c r="F517" s="11"/>
+      <c r="G517" s="12"/>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A518" s="11"/>
+      <c r="B518" s="11"/>
+      <c r="C518" s="11"/>
+      <c r="D518" s="11"/>
+      <c r="E518" s="11"/>
+      <c r="F518" s="11"/>
+      <c r="G518" s="12"/>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A519" s="11"/>
+      <c r="B519" s="11"/>
+      <c r="C519" s="11"/>
+      <c r="D519" s="11"/>
+      <c r="E519" s="11"/>
+      <c r="F519" s="11"/>
+      <c r="G519" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAE06C51-1287-4C3D-8F99-72B017C589A6}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EA92924-92A5-49A4-93CE-EF44D84367BC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="3195" yWindow="1785" windowWidth="23250" windowHeight="12450" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="266">
   <si>
     <t>Team 1</t>
   </si>
@@ -663,6 +663,177 @@
   </si>
   <si>
     <t>Vox Eminor</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2027</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2028</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2029</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2030</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2031</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2032</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2033</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2034</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2035</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2036</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2037</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2038</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2039</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2040</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2041</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2042</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2043</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2044</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2045</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2046</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2047</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2048</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2049</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2050</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2051</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2052</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2053</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2054</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2055</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2056</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2057</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2058</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2059</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2060</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2061</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2062</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2063</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2064</t>
+  </si>
+  <si>
+    <t>13x</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2065</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2066</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2067</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2068</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2069</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2070</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2071</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2072</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2073</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2074</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2075</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2076</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2077</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2078</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2079</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2080</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2081</t>
+  </si>
+  <si>
+    <t>Winamax Spanish Cirtuit 2082</t>
   </si>
 </sst>
 </file>
@@ -737,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -771,9 +942,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -789,6 +957,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1108,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:H519"/>
+  <dimension ref="A1:H533"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -10368,844 +10540,1324 @@
       <c r="H462" s="10"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A463" s="11" t="s">
+      <c r="A463" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B463" s="11" t="s">
+      <c r="B463" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C463" s="11" t="s">
+      <c r="C463" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D463" s="11" t="s">
+      <c r="D463" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E463" s="11" t="s">
+      <c r="E463" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F463" s="13">
+      <c r="F463" s="8">
         <v>46219</v>
       </c>
       <c r="G463" s="10"/>
       <c r="H463" s="10"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A464" s="11" t="s">
+      <c r="A464" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B464" s="11" t="s">
+      <c r="B464" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C464" s="11" t="s">
+      <c r="C464" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D464" s="11" t="s">
+      <c r="D464" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E464" s="11" t="s">
+      <c r="E464" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F464" s="13">
+      <c r="F464" s="8">
         <v>46219</v>
       </c>
       <c r="G464" s="10"/>
       <c r="H464" s="10"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A465" s="11" t="s">
+      <c r="A465" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B465" s="11" t="s">
+      <c r="B465" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C465" s="11" t="s">
+      <c r="C465" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D465" s="11" t="s">
+      <c r="D465" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E465" s="11"/>
-      <c r="F465" s="11"/>
+      <c r="E465" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F465" s="9">
+        <v>46219</v>
+      </c>
       <c r="G465" s="10"/>
       <c r="H465" s="10"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A466" s="11" t="s">
+      <c r="A466" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B466" s="11" t="s">
+      <c r="B466" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C466" s="11" t="s">
+      <c r="C466" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D466" s="11" t="s">
+      <c r="D466" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E466" s="11"/>
-      <c r="F466" s="11"/>
+      <c r="E466" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F466" s="9">
+        <v>46219</v>
+      </c>
       <c r="G466" s="10"/>
       <c r="H466" s="10"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A467" s="11" t="s">
+      <c r="A467" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B467" s="11" t="s">
+      <c r="B467" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C467" s="11" t="s">
+      <c r="C467" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D467" s="11" t="s">
+      <c r="D467" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E467" s="11"/>
-      <c r="F467" s="11"/>
+      <c r="E467" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F467" s="9">
+        <v>46219</v>
+      </c>
       <c r="G467" s="10"/>
       <c r="H467" s="10"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A468" s="11" t="s">
+      <c r="A468" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B468" s="11" t="s">
+      <c r="B468" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C468" s="11" t="s">
+      <c r="C468" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D468" s="11" t="s">
+      <c r="D468" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E468" s="11"/>
-      <c r="F468" s="11"/>
+      <c r="E468" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F468" s="8">
+        <v>46219</v>
+      </c>
       <c r="G468" s="10"/>
       <c r="H468" s="10"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A469" s="11" t="s">
+      <c r="A469" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B469" s="11" t="s">
+      <c r="B469" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C469" s="11" t="s">
+      <c r="C469" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D469" s="11" t="s">
+      <c r="D469" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E469" s="11"/>
-      <c r="F469" s="11"/>
+      <c r="E469" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F469" s="8">
+        <v>46219</v>
+      </c>
       <c r="G469" s="10"/>
       <c r="H469" s="10"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A470" s="11" t="s">
+      <c r="A470" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B470" s="11" t="s">
+      <c r="B470" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C470" s="11" t="s">
+      <c r="C470" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D470" s="11" t="s">
+      <c r="D470" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E470" s="11"/>
-      <c r="F470" s="11"/>
+      <c r="E470" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F470" s="8">
+        <v>46219</v>
+      </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A471" s="11" t="s">
+      <c r="A471" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B471" s="11" t="s">
+      <c r="B471" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C471" s="11" t="s">
+      <c r="C471" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D471" s="11" t="s">
+      <c r="D471" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E471" s="11"/>
-      <c r="F471" s="11"/>
+      <c r="E471" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F471" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A472" s="11" t="s">
+      <c r="A472" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B472" s="11" t="s">
+      <c r="B472" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C472" s="11" t="s">
+      <c r="C472" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D472" s="11" t="s">
+      <c r="D472" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E472" s="11"/>
-      <c r="F472" s="11"/>
+      <c r="E472" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F472" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A473" s="11" t="s">
+      <c r="A473" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B473" s="11" t="s">
+      <c r="B473" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C473" s="11" t="s">
+      <c r="C473" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D473" s="11" t="s">
+      <c r="D473" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E473" s="11"/>
-      <c r="F473" s="11"/>
+      <c r="E473" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F473" s="8">
+        <v>46219</v>
+      </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A474" s="11" t="s">
+      <c r="A474" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B474" s="11" t="s">
+      <c r="B474" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C474" s="11" t="s">
+      <c r="C474" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D474" s="11" t="s">
+      <c r="D474" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E474" s="11"/>
-      <c r="F474" s="11"/>
+      <c r="E474" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F474" s="8">
+        <v>46219</v>
+      </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A475" s="11" t="s">
+      <c r="A475" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B475" s="11" t="s">
+      <c r="B475" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C475" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D475" s="11" t="s">
+      <c r="C475" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D475" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E475" s="11"/>
-      <c r="F475" s="11"/>
+      <c r="E475" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F475" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A476" s="11" t="s">
+      <c r="A476" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B476" s="11" t="s">
+      <c r="B476" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C476" s="11" t="s">
+      <c r="C476" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D476" s="11" t="s">
+      <c r="D476" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E476" s="11"/>
-      <c r="F476" s="11"/>
+      <c r="E476" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F476" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A477" s="11" t="s">
+      <c r="A477" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B477" s="11" t="s">
+      <c r="B477" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C477" s="11" t="s">
+      <c r="C477" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D477" s="11" t="s">
+      <c r="D477" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E477" s="11"/>
-      <c r="F477" s="11"/>
+      <c r="E477" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F477" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A478" s="11" t="s">
+      <c r="A478" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B478" s="11" t="s">
+      <c r="B478" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C478" s="11" t="s">
+      <c r="C478" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D478" s="11" t="s">
+      <c r="D478" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E478" s="11"/>
-      <c r="F478" s="11"/>
+      <c r="E478" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F478" s="8">
+        <v>46220</v>
+      </c>
       <c r="G478" s="12"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A479" s="11" t="s">
+      <c r="A479" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B479" s="11" t="s">
+      <c r="B479" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C479" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D479" s="11" t="s">
+      <c r="C479" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D479" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E479" s="11"/>
-      <c r="F479" s="11"/>
+      <c r="E479" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F479" s="8">
+        <v>46220</v>
+      </c>
       <c r="G479" s="12"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A480" s="11" t="s">
+      <c r="A480" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B480" s="11" t="s">
+      <c r="B480" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C480" s="11" t="s">
+      <c r="C480" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D480" s="11" t="s">
+      <c r="D480" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E480" s="11"/>
-      <c r="F480" s="11"/>
+      <c r="E480" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F480" s="9">
+        <v>46220</v>
+      </c>
       <c r="G480" s="12"/>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A481" s="11" t="s">
+      <c r="A481" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B481" s="11" t="s">
+      <c r="B481" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C481" s="11" t="s">
+      <c r="C481" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D481" s="11" t="s">
+      <c r="D481" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E481" s="11"/>
-      <c r="F481" s="11"/>
+      <c r="E481" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F481" s="9">
+        <v>46220</v>
+      </c>
       <c r="G481" s="12"/>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A482" s="11" t="s">
+      <c r="A482" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B482" s="11" t="s">
+      <c r="B482" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C482" s="11" t="s">
+      <c r="C482" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D482" s="11" t="s">
+      <c r="D482" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E482" s="11"/>
-      <c r="F482" s="11"/>
+      <c r="E482" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F482" s="9">
+        <v>46220</v>
+      </c>
       <c r="G482" s="12"/>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A483" s="11" t="s">
+      <c r="A483" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B483" s="11" t="s">
+      <c r="B483" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C483" s="11" t="s">
+      <c r="C483" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D483" s="11" t="s">
+      <c r="D483" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E483" s="11"/>
-      <c r="F483" s="11"/>
+      <c r="E483" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F483" s="8">
+        <v>46220</v>
+      </c>
       <c r="G483" s="12"/>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A484" s="11" t="s">
+      <c r="A484" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B484" s="11" t="s">
+      <c r="B484" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C484" s="11" t="s">
+      <c r="C484" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D484" s="11" t="s">
+      <c r="D484" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E484" s="11"/>
-      <c r="F484" s="11"/>
+      <c r="E484" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F484" s="8">
+        <v>46220</v>
+      </c>
       <c r="G484" s="12"/>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A485" s="11" t="s">
+      <c r="A485" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B485" s="11" t="s">
+      <c r="B485" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C485" s="11" t="s">
+      <c r="C485" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D485" s="11" t="s">
+      <c r="D485" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E485" s="11"/>
-      <c r="F485" s="11"/>
+      <c r="E485" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F485" s="8">
+        <v>46220</v>
+      </c>
       <c r="G485" s="12"/>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A486" s="11" t="s">
+      <c r="A486" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B486" s="11" t="s">
+      <c r="B486" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C486" s="11" t="s">
+      <c r="C486" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D486" s="11" t="s">
+      <c r="D486" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E486" s="11"/>
-      <c r="F486" s="11"/>
+      <c r="E486" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F486" s="9">
+        <v>46220</v>
+      </c>
       <c r="G486" s="12"/>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A487" s="11" t="s">
+      <c r="A487" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B487" s="11" t="s">
+      <c r="B487" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C487" s="11" t="s">
+      <c r="C487" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D487" s="11" t="s">
+      <c r="D487" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E487" s="11"/>
-      <c r="F487" s="11"/>
+      <c r="E487" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F487" s="9">
+        <v>46220</v>
+      </c>
       <c r="G487" s="12"/>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A488" s="11" t="s">
+      <c r="A488" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B488" s="11" t="s">
+      <c r="B488" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C488" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D488" s="11" t="s">
+      <c r="C488" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D488" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E488" s="11"/>
-      <c r="F488" s="11"/>
+      <c r="E488" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F488" s="9">
+        <v>46220</v>
+      </c>
       <c r="G488" s="12"/>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A489" s="11" t="s">
+      <c r="A489" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B489" s="11" t="s">
+      <c r="B489" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C489" s="11" t="s">
+      <c r="C489" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D489" s="11" t="s">
+      <c r="D489" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E489" s="11"/>
-      <c r="F489" s="11"/>
+      <c r="E489" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F489" s="8">
+        <v>46220</v>
+      </c>
       <c r="G489" s="12"/>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A490" s="11" t="s">
+      <c r="A490" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B490" s="11" t="s">
+      <c r="B490" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C490" s="11" t="s">
+      <c r="C490" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D490" s="11" t="s">
+      <c r="D490" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E490" s="11"/>
-      <c r="F490" s="11"/>
+      <c r="E490" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F490" s="8">
+        <v>46220</v>
+      </c>
       <c r="G490" s="12"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A491" s="11" t="s">
+      <c r="A491" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B491" s="11" t="s">
+      <c r="B491" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C491" s="11" t="s">
+      <c r="C491" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D491" s="11" t="s">
+      <c r="D491" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E491" s="11"/>
-      <c r="F491" s="11"/>
+      <c r="E491" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F491" s="8">
+        <v>46220</v>
+      </c>
       <c r="G491" s="12"/>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A492" s="11" t="s">
+      <c r="A492" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B492" s="11" t="s">
+      <c r="B492" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C492" s="11" t="s">
+      <c r="C492" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D492" s="11" t="s">
+      <c r="D492" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E492" s="11"/>
-      <c r="F492" s="11"/>
+      <c r="E492" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F492" s="9">
+        <v>46220</v>
+      </c>
       <c r="G492" s="12"/>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A493" s="11" t="s">
+      <c r="A493" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B493" s="11" t="s">
+      <c r="B493" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C493" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D493" s="11" t="s">
+      <c r="C493" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D493" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E493" s="11"/>
-      <c r="F493" s="11"/>
+      <c r="E493" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F493" s="9">
+        <v>46220</v>
+      </c>
       <c r="G493" s="12"/>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A494" s="11" t="s">
+      <c r="A494" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B494" s="11" t="s">
+      <c r="B494" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C494" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D494" s="11" t="s">
+      <c r="C494" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D494" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E494" s="11"/>
-      <c r="F494" s="11"/>
+      <c r="E494" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F494" s="8">
+        <v>46220</v>
+      </c>
       <c r="G494" s="12"/>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A495" s="11" t="s">
+      <c r="A495" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B495" s="11" t="s">
+      <c r="B495" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C495" s="11" t="s">
+      <c r="C495" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D495" s="11" t="s">
+      <c r="D495" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E495" s="11"/>
-      <c r="F495" s="11"/>
+      <c r="E495" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F495" s="8">
+        <v>46220</v>
+      </c>
       <c r="G495" s="12"/>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A496" s="11" t="s">
+      <c r="A496" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B496" s="11" t="s">
+      <c r="B496" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C496" s="11" t="s">
+      <c r="C496" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D496" s="11" t="s">
+      <c r="D496" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E496" s="11"/>
-      <c r="F496" s="11"/>
+      <c r="E496" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F496" s="8">
+        <v>46220</v>
+      </c>
       <c r="G496" s="12"/>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A497" s="11" t="s">
+      <c r="A497" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B497" s="11" t="s">
+      <c r="B497" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C497" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D497" s="11" t="s">
+      <c r="C497" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D497" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E497" s="11"/>
-      <c r="F497" s="11"/>
+      <c r="E497" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F497" s="9">
+        <v>46221</v>
+      </c>
       <c r="G497" s="12"/>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A498" s="11" t="s">
+      <c r="A498" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B498" s="11" t="s">
+      <c r="B498" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C498" s="11" t="s">
+      <c r="C498" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D498" s="11" t="s">
+      <c r="D498" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E498" s="11"/>
-      <c r="F498" s="11"/>
+      <c r="E498" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F498" s="9">
+        <v>46221</v>
+      </c>
       <c r="G498" s="12"/>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A499" s="11" t="s">
+      <c r="A499" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B499" s="11" t="s">
+      <c r="B499" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C499" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D499" s="11" t="s">
+      <c r="C499" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D499" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E499" s="11"/>
-      <c r="F499" s="11"/>
+      <c r="E499" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F499" s="8">
+        <v>46221</v>
+      </c>
       <c r="G499" s="12"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A500" s="11" t="s">
+      <c r="A500" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B500" s="11" t="s">
+      <c r="B500" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C500" s="11" t="s">
+      <c r="C500" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D500" s="11" t="s">
+      <c r="D500" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E500" s="11"/>
-      <c r="F500" s="11"/>
+      <c r="E500" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F500" s="8">
+        <v>46221</v>
+      </c>
       <c r="G500" s="12"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A501" s="11" t="s">
+      <c r="A501" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B501" s="11" t="s">
+      <c r="B501" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C501" s="11" t="s">
+      <c r="C501" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D501" s="11" t="s">
+      <c r="D501" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E501" s="11"/>
-      <c r="F501" s="11"/>
+      <c r="E501" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F501" s="9">
+        <v>46221</v>
+      </c>
       <c r="G501" s="12"/>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A502" s="11" t="s">
+      <c r="A502" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B502" s="11" t="s">
+      <c r="B502" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C502" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D502" s="11" t="s">
+      <c r="C502" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D502" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E502" s="11"/>
-      <c r="F502" s="11"/>
+      <c r="E502" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F502" s="9">
+        <v>46221</v>
+      </c>
       <c r="G502" s="12"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A503" s="11"/>
-      <c r="B503" s="11"/>
-      <c r="C503" s="11"/>
-      <c r="D503" s="11"/>
-      <c r="E503" s="11"/>
-      <c r="F503" s="11"/>
+      <c r="A503" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C503" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E503" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F503" s="9">
+        <v>46225</v>
+      </c>
       <c r="G503" s="12"/>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A504" s="11"/>
-      <c r="B504" s="11"/>
-      <c r="C504" s="11"/>
-      <c r="D504" s="11"/>
-      <c r="E504" s="11"/>
-      <c r="F504" s="11"/>
+      <c r="A504" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E504" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F504" s="9">
+        <v>46225</v>
+      </c>
       <c r="G504" s="12"/>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A505" s="11"/>
-      <c r="B505" s="11"/>
-      <c r="C505" s="11"/>
-      <c r="D505" s="11"/>
-      <c r="E505" s="11"/>
-      <c r="F505" s="11"/>
+      <c r="A505" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E505" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F505" s="9">
+        <v>46225</v>
+      </c>
       <c r="G505" s="12"/>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A506" s="11"/>
-      <c r="B506" s="11"/>
-      <c r="C506" s="11"/>
-      <c r="D506" s="11"/>
-      <c r="E506" s="11"/>
-      <c r="F506" s="11"/>
+      <c r="A506" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E506" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F506" s="9">
+        <v>46225</v>
+      </c>
       <c r="G506" s="12"/>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A507" s="11"/>
-      <c r="B507" s="11"/>
-      <c r="C507" s="11"/>
-      <c r="D507" s="11"/>
-      <c r="E507" s="11"/>
-      <c r="F507" s="11"/>
+      <c r="A507" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E507" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F507" s="9">
+        <v>46225</v>
+      </c>
       <c r="G507" s="12"/>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A508" s="11"/>
-      <c r="B508" s="11"/>
-      <c r="C508" s="11"/>
-      <c r="D508" s="11"/>
-      <c r="E508" s="11"/>
-      <c r="F508" s="11"/>
+      <c r="A508" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E508" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F508" s="9">
+        <v>46226</v>
+      </c>
       <c r="G508" s="12"/>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A509" s="11"/>
-      <c r="B509" s="11"/>
-      <c r="C509" s="11"/>
-      <c r="D509" s="11"/>
-      <c r="E509" s="11"/>
-      <c r="F509" s="11"/>
+      <c r="A509" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E509" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F509" s="9">
+        <v>46226</v>
+      </c>
       <c r="G509" s="12"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A510" s="11"/>
-      <c r="B510" s="11"/>
-      <c r="C510" s="11"/>
-      <c r="D510" s="11"/>
-      <c r="E510" s="11"/>
-      <c r="F510" s="11"/>
+      <c r="A510" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E510" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F510" s="9">
+        <v>46226</v>
+      </c>
       <c r="G510" s="12"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A511" s="11"/>
-      <c r="B511" s="11"/>
-      <c r="C511" s="11"/>
-      <c r="D511" s="11"/>
-      <c r="E511" s="11"/>
-      <c r="F511" s="11"/>
+      <c r="A511" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D511" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E511" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F511" s="9">
+        <v>46226</v>
+      </c>
       <c r="G511" s="12"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A512" s="11"/>
-      <c r="B512" s="11"/>
-      <c r="C512" s="11"/>
-      <c r="D512" s="11"/>
-      <c r="E512" s="11"/>
-      <c r="F512" s="11"/>
+      <c r="A512" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E512" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F512" s="9">
+        <v>46226</v>
+      </c>
       <c r="G512" s="12"/>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A513" s="11"/>
-      <c r="B513" s="11"/>
-      <c r="C513" s="11"/>
-      <c r="D513" s="11"/>
-      <c r="E513" s="11"/>
-      <c r="F513" s="11"/>
+      <c r="A513" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C513" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E513" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F513" s="9">
+        <v>46226</v>
+      </c>
       <c r="G513" s="12"/>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A514" s="11"/>
-      <c r="B514" s="11"/>
-      <c r="C514" s="11"/>
-      <c r="D514" s="11"/>
-      <c r="E514" s="11"/>
-      <c r="F514" s="11"/>
+      <c r="A514" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F514" s="9">
+        <v>46226</v>
+      </c>
       <c r="G514" s="12"/>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A515" s="11"/>
-      <c r="B515" s="11"/>
-      <c r="C515" s="11"/>
-      <c r="D515" s="11"/>
-      <c r="E515" s="11"/>
-      <c r="F515" s="11"/>
+      <c r="A515" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E515" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F515" s="9">
+        <v>46227</v>
+      </c>
       <c r="G515" s="12"/>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A516" s="11"/>
-      <c r="B516" s="11"/>
-      <c r="C516" s="11"/>
-      <c r="D516" s="11"/>
-      <c r="E516" s="11"/>
-      <c r="F516" s="11"/>
+      <c r="A516" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E516" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F516" s="9">
+        <v>46227</v>
+      </c>
       <c r="G516" s="12"/>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A517" s="11"/>
-      <c r="B517" s="11"/>
-      <c r="C517" s="11"/>
-      <c r="D517" s="11"/>
-      <c r="E517" s="11"/>
-      <c r="F517" s="11"/>
+      <c r="A517" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E517" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F517" s="9">
+        <v>46227</v>
+      </c>
       <c r="G517" s="12"/>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A518" s="11"/>
-      <c r="B518" s="11"/>
-      <c r="C518" s="11"/>
-      <c r="D518" s="11"/>
-      <c r="E518" s="11"/>
-      <c r="F518" s="11"/>
+      <c r="A518" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E518" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F518" s="9">
+        <v>46227</v>
+      </c>
       <c r="G518" s="12"/>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A519" s="11"/>
-      <c r="B519" s="11"/>
-      <c r="C519" s="11"/>
-      <c r="D519" s="11"/>
-      <c r="E519" s="11"/>
-      <c r="F519" s="11"/>
+      <c r="A519" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E519" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F519" s="9">
+        <v>46227</v>
+      </c>
       <c r="G519" s="12"/>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A520" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E520" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F520" s="9">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A521" s="11"/>
+      <c r="B521" s="11"/>
+      <c r="C521" s="11"/>
+      <c r="D521" s="11"/>
+      <c r="E521" s="11"/>
+      <c r="F521" s="11"/>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A522" s="11"/>
+      <c r="B522" s="11"/>
+      <c r="C522" s="11"/>
+      <c r="D522" s="11"/>
+      <c r="E522" s="11"/>
+      <c r="F522" s="11"/>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A523" s="11"/>
+      <c r="B523" s="11"/>
+      <c r="C523" s="11"/>
+      <c r="D523" s="11"/>
+      <c r="E523" s="11"/>
+      <c r="F523" s="11"/>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A524" s="11"/>
+      <c r="B524" s="11"/>
+      <c r="C524" s="11"/>
+      <c r="D524" s="11"/>
+      <c r="E524" s="11"/>
+      <c r="F524" s="11"/>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A525" s="11"/>
+      <c r="B525" s="11"/>
+      <c r="C525" s="11"/>
+      <c r="D525" s="11"/>
+      <c r="E525" s="11"/>
+      <c r="F525" s="11"/>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A526" s="11"/>
+      <c r="B526" s="11"/>
+      <c r="C526" s="11"/>
+      <c r="D526" s="11"/>
+      <c r="E526" s="11"/>
+      <c r="F526" s="11"/>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A527" s="11"/>
+      <c r="B527" s="11"/>
+      <c r="C527" s="11"/>
+      <c r="D527" s="11"/>
+      <c r="E527" s="11"/>
+      <c r="F527" s="11"/>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A528" s="11"/>
+      <c r="B528" s="11"/>
+      <c r="C528" s="11"/>
+      <c r="D528" s="11"/>
+      <c r="E528" s="11"/>
+      <c r="F528" s="11"/>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A529" s="11"/>
+      <c r="B529" s="11"/>
+      <c r="C529" s="11"/>
+      <c r="D529" s="11"/>
+      <c r="E529" s="11"/>
+      <c r="F529" s="11"/>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A530" s="11"/>
+      <c r="B530" s="11"/>
+      <c r="C530" s="11"/>
+      <c r="D530" s="11"/>
+      <c r="E530" s="11"/>
+      <c r="F530" s="11"/>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A531" s="11"/>
+      <c r="B531" s="11"/>
+      <c r="C531" s="11"/>
+      <c r="D531" s="11"/>
+      <c r="E531" s="11"/>
+      <c r="F531" s="11"/>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A532" s="11"/>
+      <c r="B532" s="11"/>
+      <c r="C532" s="11"/>
+      <c r="D532" s="11"/>
+      <c r="E532" s="11"/>
+      <c r="F532" s="11"/>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A533" s="11"/>
+      <c r="B533" s="11"/>
+      <c r="C533" s="11"/>
+      <c r="D533" s="11"/>
+      <c r="E533" s="11"/>
+      <c r="F533" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EA92924-92A5-49A4-93CE-EF44D84367BC}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875A5B4F-0713-4E80-888F-0BBE7E743135}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="1785" windowWidth="23250" windowHeight="12450" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="2520" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="268">
   <si>
     <t>Team 1</t>
   </si>
@@ -834,6 +834,12 @@
   </si>
   <si>
     <t>Winamax Spanish Cirtuit 2082</t>
+  </si>
+  <si>
+    <t>BLAST Premier 2026 Seoul</t>
+  </si>
+  <si>
+    <t>Lux Tenebris</t>
   </si>
 </sst>
 </file>
@@ -957,10 +963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1280,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:H533"/>
+  <dimension ref="A1:H606"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -11379,43 +11381,43 @@
       <c r="G502" s="12"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A503" s="4" t="s">
+      <c r="A503" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B503" s="4" t="s">
+      <c r="B503" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C503" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D503" s="4" t="s">
+      <c r="C503" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D503" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E503" s="4" t="s">
+      <c r="E503" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F503" s="9">
+      <c r="F503" s="8">
         <v>46225</v>
       </c>
       <c r="G503" s="12"/>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A504" s="4" t="s">
+      <c r="A504" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B504" s="4" t="s">
+      <c r="B504" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C504" s="4" t="s">
+      <c r="C504" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D504" s="4" t="s">
+      <c r="D504" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E504" s="4" t="s">
+      <c r="E504" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F504" s="9">
+      <c r="F504" s="8">
         <v>46225</v>
       </c>
       <c r="G504" s="12"/>
@@ -11484,43 +11486,43 @@
       <c r="G507" s="12"/>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A508" s="4" t="s">
+      <c r="A508" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B508" s="4" t="s">
+      <c r="B508" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C508" s="4" t="s">
+      <c r="C508" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D508" s="4" t="s">
+      <c r="D508" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E508" s="4" t="s">
+      <c r="E508" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F508" s="9">
+      <c r="F508" s="8">
         <v>46226</v>
       </c>
       <c r="G508" s="12"/>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A509" s="4" t="s">
+      <c r="A509" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B509" s="4" t="s">
+      <c r="B509" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C509" s="4" t="s">
+      <c r="C509" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D509" s="4" t="s">
+      <c r="D509" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E509" s="4" t="s">
+      <c r="E509" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="F509" s="9">
+      <c r="F509" s="8">
         <v>46226</v>
       </c>
       <c r="G509" s="12"/>
@@ -11568,64 +11570,64 @@
       <c r="G511" s="12"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A512" s="4" t="s">
+      <c r="A512" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B512" s="4" t="s">
+      <c r="B512" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C512" s="4" t="s">
+      <c r="C512" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D512" s="4" t="s">
+      <c r="D512" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E512" s="4" t="s">
+      <c r="E512" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="F512" s="9">
+      <c r="F512" s="8">
         <v>46226</v>
       </c>
       <c r="G512" s="12"/>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A513" s="4" t="s">
+      <c r="A513" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B513" s="4" t="s">
+      <c r="B513" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C513" s="4" t="s">
+      <c r="C513" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D513" s="4" t="s">
+      <c r="D513" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E513" s="4" t="s">
+      <c r="E513" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="F513" s="9">
+      <c r="F513" s="8">
         <v>46226</v>
       </c>
       <c r="G513" s="12"/>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A514" s="4" t="s">
+      <c r="A514" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B514" s="4" t="s">
+      <c r="B514" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C514" s="4" t="s">
+      <c r="C514" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D514" s="4" t="s">
+      <c r="D514" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E514" s="4" t="s">
+      <c r="E514" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="F514" s="9">
+      <c r="F514" s="8">
         <v>46226</v>
       </c>
       <c r="G514" s="12"/>
@@ -11673,43 +11675,43 @@
       <c r="G516" s="12"/>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A517" s="4" t="s">
+      <c r="A517" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B517" s="4" t="s">
+      <c r="B517" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C517" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D517" s="4" t="s">
+      <c r="C517" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D517" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E517" s="4" t="s">
+      <c r="E517" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F517" s="9">
+      <c r="F517" s="8">
         <v>46227</v>
       </c>
       <c r="G517" s="12"/>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A518" s="4" t="s">
+      <c r="A518" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B518" s="4" t="s">
+      <c r="B518" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C518" s="4" t="s">
+      <c r="C518" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D518" s="4" t="s">
+      <c r="D518" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E518" s="4" t="s">
+      <c r="E518" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="F518" s="9">
+      <c r="F518" s="8">
         <v>46227</v>
       </c>
       <c r="G518" s="12"/>
@@ -11756,108 +11758,1136 @@
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A521" s="11"/>
-      <c r="B521" s="11"/>
-      <c r="C521" s="11"/>
-      <c r="D521" s="11"/>
-      <c r="E521" s="11"/>
-      <c r="F521" s="11"/>
+      <c r="A521" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D521" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E521" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F521" s="8">
+        <v>46235</v>
+      </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A522" s="11"/>
-      <c r="B522" s="11"/>
-      <c r="C522" s="11"/>
-      <c r="D522" s="11"/>
-      <c r="E522" s="11"/>
-      <c r="F522" s="11"/>
+      <c r="A522" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D522" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E522" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F522" s="8">
+        <v>46235</v>
+      </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A523" s="11"/>
-      <c r="B523" s="11"/>
-      <c r="C523" s="11"/>
-      <c r="D523" s="11"/>
-      <c r="E523" s="11"/>
-      <c r="F523" s="11"/>
+      <c r="A523" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D523" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E523" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F523" s="8">
+        <v>46235</v>
+      </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A524" s="11"/>
-      <c r="B524" s="11"/>
-      <c r="C524" s="11"/>
-      <c r="D524" s="11"/>
-      <c r="E524" s="11"/>
-      <c r="F524" s="11"/>
+      <c r="A524" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E524" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F524" s="9">
+        <v>46235</v>
+      </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A525" s="11"/>
-      <c r="B525" s="11"/>
-      <c r="C525" s="11"/>
-      <c r="D525" s="11"/>
-      <c r="E525" s="11"/>
-      <c r="F525" s="11"/>
+      <c r="A525" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E525" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F525" s="9">
+        <v>46235</v>
+      </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A526" s="11"/>
-      <c r="B526" s="11"/>
-      <c r="C526" s="11"/>
-      <c r="D526" s="11"/>
-      <c r="E526" s="11"/>
-      <c r="F526" s="11"/>
+      <c r="A526" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D526" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E526" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F526" s="8">
+        <v>46236</v>
+      </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A527" s="11"/>
-      <c r="B527" s="11"/>
-      <c r="C527" s="11"/>
-      <c r="D527" s="11"/>
-      <c r="E527" s="11"/>
-      <c r="F527" s="11"/>
+      <c r="A527" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E527" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F527" s="8">
+        <v>46236</v>
+      </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A528" s="11"/>
-      <c r="B528" s="11"/>
-      <c r="C528" s="11"/>
-      <c r="D528" s="11"/>
-      <c r="E528" s="11"/>
-      <c r="F528" s="11"/>
+      <c r="A528" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D528" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E528" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F528" s="8">
+        <v>46236</v>
+      </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A529" s="11"/>
-      <c r="B529" s="11"/>
-      <c r="C529" s="11"/>
-      <c r="D529" s="11"/>
-      <c r="E529" s="11"/>
-      <c r="F529" s="11"/>
+      <c r="A529" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E529" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F529" s="9">
+        <v>46236</v>
+      </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A530" s="11"/>
-      <c r="B530" s="11"/>
-      <c r="C530" s="11"/>
-      <c r="D530" s="11"/>
-      <c r="E530" s="11"/>
-      <c r="F530" s="11"/>
+      <c r="A530" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E530" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F530" s="9">
+        <v>46236</v>
+      </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A531" s="11"/>
-      <c r="B531" s="11"/>
-      <c r="C531" s="11"/>
-      <c r="D531" s="11"/>
-      <c r="E531" s="11"/>
-      <c r="F531" s="11"/>
+      <c r="A531" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E531" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F531" s="8">
+        <v>46237</v>
+      </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A532" s="11"/>
-      <c r="B532" s="11"/>
-      <c r="C532" s="11"/>
-      <c r="D532" s="11"/>
-      <c r="E532" s="11"/>
-      <c r="F532" s="11"/>
+      <c r="A532" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D532" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E532" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F532" s="8">
+        <v>46237</v>
+      </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A533" s="11"/>
-      <c r="B533" s="11"/>
-      <c r="C533" s="11"/>
-      <c r="D533" s="11"/>
-      <c r="E533" s="11"/>
-      <c r="F533" s="11"/>
+      <c r="A533" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E533" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F533" s="9">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A534" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E534" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F534" s="9">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A535" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D535" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E535" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F535" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A536" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D536" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E536" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F536" s="8">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A537" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C537" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E537" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F537" s="9">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A538" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E538" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F538" s="9">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A539" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E539" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F539" s="9">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A540" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D540" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E540" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F540" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A541" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E541" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F541" s="8">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A542" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E542" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F542" s="9">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A543" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E543" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F543" s="9">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A544" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E544" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F544" s="9">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A545" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D545" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E545" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F545" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A546" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D546" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E546" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F546" s="8">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A547" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C547" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E547" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F547" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A548" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C548" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E548" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F548" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A549" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C549" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E549" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F549" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A550" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D550" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E550" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F550" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A551" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D551" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E551" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F551" s="8">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A552" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E552" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F552" s="9">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A553" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E553" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F553" s="9">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A554" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D554" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E554" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F554" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A555" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D555" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E555" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F555" s="8">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A556" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E556" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F556" s="9">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A557" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C557" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E557" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F557" s="9">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A558" s="11"/>
+      <c r="B558" s="11"/>
+      <c r="C558" s="11"/>
+      <c r="D558" s="11"/>
+      <c r="E558" s="11"/>
+      <c r="F558" s="11"/>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A559" s="11"/>
+      <c r="B559" s="11"/>
+      <c r="C559" s="11"/>
+      <c r="D559" s="11"/>
+      <c r="E559" s="11"/>
+      <c r="F559" s="11"/>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A560" s="11"/>
+      <c r="B560" s="11"/>
+      <c r="C560" s="11"/>
+      <c r="D560" s="11"/>
+      <c r="E560" s="11"/>
+      <c r="F560" s="11"/>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A561" s="11"/>
+      <c r="B561" s="11"/>
+      <c r="C561" s="11"/>
+      <c r="D561" s="11"/>
+      <c r="E561" s="11"/>
+      <c r="F561" s="11"/>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A562" s="11"/>
+      <c r="B562" s="11"/>
+      <c r="C562" s="11"/>
+      <c r="D562" s="11"/>
+      <c r="E562" s="11"/>
+      <c r="F562" s="11"/>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A563" s="11"/>
+      <c r="B563" s="11"/>
+      <c r="C563" s="11"/>
+      <c r="D563" s="11"/>
+      <c r="E563" s="11"/>
+      <c r="F563" s="11"/>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A564" s="11"/>
+      <c r="B564" s="11"/>
+      <c r="C564" s="11"/>
+      <c r="D564" s="11"/>
+      <c r="E564" s="11"/>
+      <c r="F564" s="11"/>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A565" s="11"/>
+      <c r="B565" s="11"/>
+      <c r="C565" s="11"/>
+      <c r="D565" s="11"/>
+      <c r="E565" s="11"/>
+      <c r="F565" s="11"/>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A566" s="11"/>
+      <c r="B566" s="11"/>
+      <c r="C566" s="11"/>
+      <c r="D566" s="11"/>
+      <c r="E566" s="11"/>
+      <c r="F566" s="11"/>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A567" s="11"/>
+      <c r="B567" s="11"/>
+      <c r="C567" s="11"/>
+      <c r="D567" s="11"/>
+      <c r="E567" s="11"/>
+      <c r="F567" s="11"/>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A568" s="11"/>
+      <c r="B568" s="11"/>
+      <c r="C568" s="11"/>
+      <c r="D568" s="11"/>
+      <c r="E568" s="11"/>
+      <c r="F568" s="11"/>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A569" s="11"/>
+      <c r="B569" s="11"/>
+      <c r="C569" s="11"/>
+      <c r="D569" s="11"/>
+      <c r="E569" s="11"/>
+      <c r="F569" s="11"/>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A570" s="11"/>
+      <c r="B570" s="11"/>
+      <c r="C570" s="11"/>
+      <c r="D570" s="11"/>
+      <c r="E570" s="11"/>
+      <c r="F570" s="11"/>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A571" s="11"/>
+      <c r="B571" s="11"/>
+      <c r="C571" s="11"/>
+      <c r="D571" s="11"/>
+      <c r="E571" s="11"/>
+      <c r="F571" s="11"/>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A572" s="11"/>
+      <c r="B572" s="11"/>
+      <c r="C572" s="11"/>
+      <c r="D572" s="11"/>
+      <c r="E572" s="11"/>
+      <c r="F572" s="11"/>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A573" s="11"/>
+      <c r="B573" s="11"/>
+      <c r="C573" s="11"/>
+      <c r="D573" s="11"/>
+      <c r="E573" s="11"/>
+      <c r="F573" s="11"/>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A574" s="11"/>
+      <c r="B574" s="11"/>
+      <c r="C574" s="11"/>
+      <c r="D574" s="11"/>
+      <c r="E574" s="11"/>
+      <c r="F574" s="11"/>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A575" s="11"/>
+      <c r="B575" s="11"/>
+      <c r="C575" s="11"/>
+      <c r="D575" s="11"/>
+      <c r="E575" s="11"/>
+      <c r="F575" s="11"/>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A576" s="11"/>
+      <c r="B576" s="11"/>
+      <c r="C576" s="11"/>
+      <c r="D576" s="11"/>
+      <c r="E576" s="11"/>
+      <c r="F576" s="11"/>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A577" s="11"/>
+      <c r="B577" s="11"/>
+      <c r="C577" s="11"/>
+      <c r="D577" s="11"/>
+      <c r="E577" s="11"/>
+      <c r="F577" s="11"/>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A578" s="11"/>
+      <c r="B578" s="11"/>
+      <c r="C578" s="11"/>
+      <c r="D578" s="11"/>
+      <c r="E578" s="11"/>
+      <c r="F578" s="11"/>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A579" s="11"/>
+      <c r="B579" s="11"/>
+      <c r="C579" s="11"/>
+      <c r="D579" s="11"/>
+      <c r="E579" s="11"/>
+      <c r="F579" s="11"/>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A580" s="11"/>
+      <c r="B580" s="11"/>
+      <c r="C580" s="11"/>
+      <c r="D580" s="11"/>
+      <c r="E580" s="11"/>
+      <c r="F580" s="11"/>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A581" s="11"/>
+      <c r="B581" s="11"/>
+      <c r="C581" s="11"/>
+      <c r="D581" s="11"/>
+      <c r="E581" s="11"/>
+      <c r="F581" s="11"/>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A582" s="11"/>
+      <c r="B582" s="11"/>
+      <c r="C582" s="11"/>
+      <c r="D582" s="11"/>
+      <c r="E582" s="11"/>
+      <c r="F582" s="11"/>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A583" s="11"/>
+      <c r="B583" s="11"/>
+      <c r="C583" s="11"/>
+      <c r="D583" s="11"/>
+      <c r="E583" s="11"/>
+      <c r="F583" s="11"/>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A584" s="11"/>
+      <c r="B584" s="11"/>
+      <c r="C584" s="11"/>
+      <c r="D584" s="11"/>
+      <c r="E584" s="11"/>
+      <c r="F584" s="11"/>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A585" s="11"/>
+      <c r="B585" s="11"/>
+      <c r="C585" s="11"/>
+      <c r="D585" s="11"/>
+      <c r="E585" s="11"/>
+      <c r="F585" s="11"/>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A586" s="11"/>
+      <c r="B586" s="11"/>
+      <c r="C586" s="11"/>
+      <c r="D586" s="11"/>
+      <c r="E586" s="11"/>
+      <c r="F586" s="11"/>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A587" s="11"/>
+      <c r="B587" s="11"/>
+      <c r="C587" s="11"/>
+      <c r="D587" s="11"/>
+      <c r="E587" s="11"/>
+      <c r="F587" s="11"/>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A588" s="11"/>
+      <c r="B588" s="11"/>
+      <c r="C588" s="11"/>
+      <c r="D588" s="11"/>
+      <c r="E588" s="11"/>
+      <c r="F588" s="11"/>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A589" s="11"/>
+      <c r="B589" s="11"/>
+      <c r="C589" s="11"/>
+      <c r="D589" s="11"/>
+      <c r="E589" s="11"/>
+      <c r="F589" s="11"/>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A590" s="11"/>
+      <c r="B590" s="11"/>
+      <c r="C590" s="11"/>
+      <c r="D590" s="11"/>
+      <c r="E590" s="11"/>
+      <c r="F590" s="11"/>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A591" s="11"/>
+      <c r="B591" s="11"/>
+      <c r="C591" s="11"/>
+      <c r="D591" s="11"/>
+      <c r="E591" s="11"/>
+      <c r="F591" s="11"/>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A592" s="11"/>
+      <c r="B592" s="11"/>
+      <c r="C592" s="11"/>
+      <c r="D592" s="11"/>
+      <c r="E592" s="11"/>
+      <c r="F592" s="11"/>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A593" s="11"/>
+      <c r="B593" s="11"/>
+      <c r="C593" s="11"/>
+      <c r="D593" s="11"/>
+      <c r="E593" s="11"/>
+      <c r="F593" s="11"/>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A594" s="11"/>
+      <c r="B594" s="11"/>
+      <c r="C594" s="11"/>
+      <c r="D594" s="11"/>
+      <c r="E594" s="11"/>
+      <c r="F594" s="11"/>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A595" s="11"/>
+      <c r="B595" s="11"/>
+      <c r="C595" s="11"/>
+      <c r="D595" s="11"/>
+      <c r="E595" s="11"/>
+      <c r="F595" s="11"/>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A596" s="11"/>
+      <c r="B596" s="11"/>
+      <c r="C596" s="11"/>
+      <c r="D596" s="11"/>
+      <c r="E596" s="11"/>
+      <c r="F596" s="11"/>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A597" s="11"/>
+      <c r="B597" s="11"/>
+      <c r="C597" s="11"/>
+      <c r="D597" s="11"/>
+      <c r="E597" s="11"/>
+      <c r="F597" s="11"/>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A598" s="11"/>
+      <c r="B598" s="11"/>
+      <c r="C598" s="11"/>
+      <c r="D598" s="11"/>
+      <c r="E598" s="11"/>
+      <c r="F598" s="11"/>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A599" s="11"/>
+      <c r="B599" s="11"/>
+      <c r="C599" s="11"/>
+      <c r="D599" s="11"/>
+      <c r="E599" s="11"/>
+      <c r="F599" s="11"/>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A600" s="11"/>
+      <c r="B600" s="11"/>
+      <c r="C600" s="11"/>
+      <c r="D600" s="11"/>
+      <c r="E600" s="11"/>
+      <c r="F600" s="11"/>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A601" s="11"/>
+      <c r="B601" s="11"/>
+      <c r="C601" s="11"/>
+      <c r="D601" s="11"/>
+      <c r="E601" s="11"/>
+      <c r="F601" s="11"/>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A602" s="11"/>
+      <c r="B602" s="11"/>
+      <c r="C602" s="11"/>
+      <c r="D602" s="11"/>
+      <c r="E602" s="11"/>
+      <c r="F602" s="11"/>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A603" s="11"/>
+      <c r="B603" s="11"/>
+      <c r="C603" s="11"/>
+      <c r="D603" s="11"/>
+      <c r="E603" s="11"/>
+      <c r="F603" s="11"/>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A604" s="11"/>
+      <c r="B604" s="11"/>
+      <c r="C604" s="11"/>
+      <c r="D604" s="11"/>
+      <c r="E604" s="11"/>
+      <c r="F604" s="11"/>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A605" s="11"/>
+      <c r="B605" s="11"/>
+      <c r="C605" s="11"/>
+      <c r="D605" s="11"/>
+      <c r="E605" s="11"/>
+      <c r="F605" s="11"/>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A606" s="11"/>
+      <c r="B606" s="11"/>
+      <c r="C606" s="11"/>
+      <c r="D606" s="11"/>
+      <c r="E606" s="11"/>
+      <c r="F606" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
